--- a/public/downloads/primary-reanalysis.xlsx
+++ b/public/downloads/primary-reanalysis.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R337cc99666494079"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Results" sheetId="2" r:id="R2df2cf3237574a68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Outcomes" sheetId="3" r:id="Ra1dd578ad53845b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Mean Differences" sheetId="4" r:id="R8de45a11742e4922"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta-regression" sheetId="5" r:id="R24c8c88189ae4795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amyloid Mapping" sheetId="6" r:id="R76d84ba44dda4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reproduction Check" sheetId="7" r:id="R503073ba09704319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleaned Rows" sheetId="8" r:id="Rc2a8d8e327fc4586"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="R634feb7a1eb04adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R6f9f4c6019b44125"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Results" sheetId="2" r:id="R1f5a7edd44304061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Outcomes" sheetId="3" r:id="R082a750eaaba43d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw Mean Differences" sheetId="4" r:id="Rc961517c89d04ca5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta-regression" sheetId="5" r:id="R74ef8ed9b87e4f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Amyloid Mapping" sheetId="6" r:id="R5ec1824c880e499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reproduction Check" sheetId="7" r:id="R4c4a4339bd094f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cleaned Rows" sheetId="8" r:id="Rdb39be7c0af54f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="9" r:id="Rf8ebf87b84294505"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -575,7 +575,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf21fe890124f49b7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f654f010c644782"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -620,7 +620,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AllOutcomesTable" displayName="AllOutcomesTable" ref="A4:K134" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="AllOutcomesTable" displayName="AllOutcomesTable" ref="A4:K151" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Outcome"/>
@@ -639,7 +639,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RawMDTable" displayName="RawMDTable" ref="A4:J37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="RawMDTable" displayName="RawMDTable" ref="A4:J40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Outcome"/>
@@ -1707,9 +1707,9 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5752e84e02f042dc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ce5eebd7b71459e"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R611257f3ae2c47c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R313036861b254385"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1962,7 +1962,7 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D10" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E10" s="40" t="n">
         <x:v>2</x:v>
@@ -1997,62 +1997,62 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D11" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E11" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F11" s="43" t="n">
-        <x:v>-0.584878</x:v>
+        <x:v>-0.2134511150771982</x:v>
       </x:c>
       <x:c r="G11" s="43" t="n">
-        <x:v>-1.204363816593575</x:v>
+        <x:v>-0.8099558948678978</x:v>
       </x:c>
       <x:c r="H11" s="43" t="n">
-        <x:v>0.03460781659357481</x:v>
+        <x:v>0.3830536647135014</x:v>
       </x:c>
       <x:c r="I11" s="46" t="n">
-        <x:v>0.06424586215544333</x:v>
+        <x:v>0.4830868444649154</x:v>
       </x:c>
       <x:c r="J11" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="49"/>
+        <x:v>0.1306834223944999</x:v>
+      </x:c>
+      <x:c r="K11" s="49" t="n">
+        <x:v>67.81723560627916</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="37" t="str">
-        <x:v>1.3</x:v>
+        <x:v>1.2</x:v>
       </x:c>
       <x:c r="B12" s="37" t="str">
-        <x:v>ADAS-Cog scale above 24 months</x:v>
+        <x:v>ADAS-Cog scale at 24 months</x:v>
       </x:c>
       <x:c r="C12" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D12" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E12" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="43" t="n">
-        <x:v>-0.1176549874200436</x:v>
+        <x:v>-0.584878</x:v>
       </x:c>
       <x:c r="G12" s="43" t="n">
-        <x:v>-0.2063118610737351</x:v>
+        <x:v>-1.204363816593575</x:v>
       </x:c>
       <x:c r="H12" s="43" t="n">
-        <x:v>-0.02899811376635203</x:v>
+        <x:v>0.03460781659357481</x:v>
       </x:c>
       <x:c r="I12" s="46" t="n">
-        <x:v>0.009294325651543764</x:v>
+        <x:v>0.06424586215544333</x:v>
       </x:c>
       <x:c r="J12" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K12" s="49"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="37" t="str">
@@ -2065,7 +2065,7 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D13" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E13" s="40" t="n">
         <x:v>2</x:v>
@@ -2091,72 +2091,72 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="37" t="str">
-        <x:v>1.4</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="B14" s="37" t="str">
-        <x:v>MMSE scale at 18 months</x:v>
+        <x:v>ADAS-Cog scale above 24 months</x:v>
       </x:c>
       <x:c r="C14" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D14" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E14" s="40" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="43" t="n">
-        <x:v>0.1016834060990106</x:v>
+        <x:v>-0.1176549874200436</x:v>
       </x:c>
       <x:c r="G14" s="43" t="n">
-        <x:v>0.01393113150845662</x:v>
+        <x:v>-0.2063118610737351</x:v>
       </x:c>
       <x:c r="H14" s="43" t="n">
-        <x:v>0.1894356806895645</x:v>
+        <x:v>-0.02899811376635203</x:v>
       </x:c>
       <x:c r="I14" s="46" t="n">
-        <x:v>0.02974714085040944</x:v>
+        <x:v>0.009294325651543764</x:v>
       </x:c>
       <x:c r="J14" s="43" t="n">
-        <x:v>0.000003620021494365027</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="49" t="n">
-        <x:v>0.05388317723724705</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="37" t="str">
-        <x:v>1.4</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="B15" s="37" t="str">
-        <x:v>MMSE scale at 18 months</x:v>
+        <x:v>ADAS-Cog scale above 24 months</x:v>
       </x:c>
       <x:c r="C15" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D15" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E15" s="40" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F15" s="43" t="n">
-        <x:v>0.1147957028524519</x:v>
+        <x:v>-0.1176549874200436</x:v>
       </x:c>
       <x:c r="G15" s="43" t="n">
-        <x:v>0.04137632887883533</x:v>
+        <x:v>-0.2063118610737351</x:v>
       </x:c>
       <x:c r="H15" s="43" t="n">
-        <x:v>0.1882150768260684</x:v>
+        <x:v>-0.02899811376635203</x:v>
       </x:c>
       <x:c r="I15" s="46" t="n">
-        <x:v>0.007682938339376558</x:v>
+        <x:v>0.009294325651543764</x:v>
       </x:c>
       <x:c r="J15" s="43" t="n">
-        <x:v>0.00000197168644518212</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="49" t="n">
-        <x:v>0.03456161596491084</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2170,27 +2170,29 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D16" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E16" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F16" s="43" t="n">
-        <x:v>0.1455607115873234</x:v>
+        <x:v>0.1016834060990106</x:v>
       </x:c>
       <x:c r="G16" s="43" t="n">
-        <x:v>0.03559766079525874</x:v>
+        <x:v>0.01393113150845662</x:v>
       </x:c>
       <x:c r="H16" s="43" t="n">
-        <x:v>0.2555237623793881</x:v>
+        <x:v>0.1894356806895645</x:v>
       </x:c>
       <x:c r="I16" s="46" t="n">
-        <x:v>0.009474210427497175</x:v>
+        <x:v>0.02974714085040944</x:v>
       </x:c>
       <x:c r="J16" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="49"/>
+        <x:v>0.000003620021494365027</x:v>
+      </x:c>
+      <x:c r="K16" s="49" t="n">
+        <x:v>0.05388317723724705</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="37" t="str">
@@ -2203,28 +2205,28 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D17" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E17" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F17" s="43" t="n">
-        <x:v>0.09558999252506314</x:v>
+        <x:v>0.1147957028524519</x:v>
       </x:c>
       <x:c r="G17" s="43" t="n">
-        <x:v>-0.05239698184162078</x:v>
+        <x:v>0.04137632887883533</x:v>
       </x:c>
       <x:c r="H17" s="43" t="n">
-        <x:v>0.2435769668917471</x:v>
+        <x:v>0.1882150768260684</x:v>
       </x:c>
       <x:c r="I17" s="46" t="n">
-        <x:v>0.132045274196092</x:v>
+        <x:v>0.007682938339376558</x:v>
       </x:c>
       <x:c r="J17" s="43" t="n">
-        <x:v>0.002954786261643479</x:v>
+        <x:v>0.00000197168644518212</x:v>
       </x:c>
       <x:c r="K17" s="49" t="n">
-        <x:v>32.43299052474023</x:v>
+        <x:v>0.03456161596491084</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2238,305 +2240,303 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D18" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E18" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F18" s="43" t="n">
-        <x:v>0.1026725257995174</x:v>
+        <x:v>0.1455607115873234</x:v>
       </x:c>
       <x:c r="G18" s="43" t="n">
-        <x:v>-0.1593302841719179</x:v>
+        <x:v>0.03559766079525874</x:v>
       </x:c>
       <x:c r="H18" s="43" t="n">
-        <x:v>0.3646753357709526</x:v>
+        <x:v>0.2555237623793881</x:v>
       </x:c>
       <x:c r="I18" s="46" t="n">
-        <x:v>0.2338221182650312</x:v>
+        <x:v>0.009474210427497175</x:v>
       </x:c>
       <x:c r="J18" s="43" t="n">
-        <x:v>0.005255837247598882</x:v>
-      </x:c>
-      <x:c r="K18" s="49" t="n">
-        <x:v>50.20276544932284</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="49"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="37" t="str">
-        <x:v>1.5</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="B19" s="37" t="str">
-        <x:v>MMSE scale at 24 months</x:v>
+        <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C19" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D19" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E19" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F19" s="43" t="n">
-        <x:v>-0.04142837216421257</x:v>
+        <x:v>0.09558999252506314</x:v>
       </x:c>
       <x:c r="G19" s="43" t="n">
-        <x:v>-0.3070308965575574</x:v>
+        <x:v>-0.05239698184162078</x:v>
       </x:c>
       <x:c r="H19" s="43" t="n">
-        <x:v>0.2241741522291322</x:v>
+        <x:v>0.2435769668917471</x:v>
       </x:c>
       <x:c r="I19" s="46" t="n">
-        <x:v>0.7598232522121194</x:v>
+        <x:v>0.132045274196092</x:v>
       </x:c>
       <x:c r="J19" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.002954786261643479</x:v>
       </x:c>
       <x:c r="K19" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>32.43299052474023</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="37" t="str">
-        <x:v>1.5</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="B20" s="37" t="str">
-        <x:v>MMSE scale at 24 months</x:v>
+        <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C20" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D20" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E20" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F20" s="43" t="n">
-        <x:v>0.184919</x:v>
+        <x:v>0.1026725257995174</x:v>
       </x:c>
       <x:c r="G20" s="43" t="n">
-        <x:v>-0.4267622400071364</x:v>
+        <x:v>-0.1593302841719179</x:v>
       </x:c>
       <x:c r="H20" s="43" t="n">
-        <x:v>0.7966002400071364</x:v>
+        <x:v>0.3646753357709526</x:v>
       </x:c>
       <x:c r="I20" s="46" t="n">
-        <x:v>0.5535011059778423</x:v>
+        <x:v>0.2338221182650312</x:v>
       </x:c>
       <x:c r="J20" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K20" s="49"/>
+        <x:v>0.005255837247598882</x:v>
+      </x:c>
+      <x:c r="K20" s="49" t="n">
+        <x:v>50.20276544932284</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="37" t="str">
-        <x:v>1.6</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="B21" s="37" t="str">
-        <x:v>ADAS-Cog 24 months mean difference</x:v>
+        <x:v>MMSE scale at 24 months</x:v>
       </x:c>
       <x:c r="C21" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D21" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E21" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="43" t="n">
-        <x:v>-1.405503778337532</x:v>
+        <x:v>-0.04142837216421257</x:v>
       </x:c>
       <x:c r="G21" s="43" t="n">
-        <x:v>-5.245306413837063</x:v>
+        <x:v>-0.3070308965575574</x:v>
       </x:c>
       <x:c r="H21" s="43" t="n">
-        <x:v>2.434298857161997</x:v>
+        <x:v>0.2241741522291322</x:v>
       </x:c>
       <x:c r="I21" s="46" t="n">
-        <x:v>0.4731172993008963</x:v>
+        <x:v>0.7598232522121194</x:v>
       </x:c>
       <x:c r="J21" s="43" t="n">
-        <x:v>5.423950000000001</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K21" s="49" t="n">
-        <x:v>68.82792226332252</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="37" t="str">
-        <x:v>1.6</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="B22" s="37" t="str">
-        <x:v>ADAS-Cog 24 months mean difference</x:v>
+        <x:v>MMSE scale at 24 months</x:v>
       </x:c>
       <x:c r="C22" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D22" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E22" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F22" s="43" t="n">
-        <x:v>-3.71</x:v>
+        <x:v>-0.04142837216421257</x:v>
       </x:c>
       <x:c r="G22" s="43" t="n">
-        <x:v>-7.492730490162304</x:v>
+        <x:v>-0.3070308965575574</x:v>
       </x:c>
       <x:c r="H22" s="43" t="n">
-        <x:v>0.07273049016230448</x:v>
+        <x:v>0.2241741522291322</x:v>
       </x:c>
       <x:c r="I22" s="46" t="n">
-        <x:v>0.05457056124297725</x:v>
+        <x:v>0.7598232522121194</x:v>
       </x:c>
       <x:c r="J22" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="49"/>
+      <x:c r="K22" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="37" t="str">
-        <x:v>2.1</x:v>
+        <x:v>1.5</x:v>
       </x:c>
       <x:c r="B23" s="37" t="str">
-        <x:v>CDR-SB scale at 18 months</x:v>
+        <x:v>MMSE scale at 24 months</x:v>
       </x:c>
       <x:c r="C23" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D23" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E23" s="40" t="n">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="43" t="n">
-        <x:v>-0.1368236744489688</x:v>
+        <x:v>0.184919</x:v>
       </x:c>
       <x:c r="G23" s="43" t="n">
-        <x:v>-0.279188648002032</x:v>
+        <x:v>-0.4267622400071364</x:v>
       </x:c>
       <x:c r="H23" s="43" t="n">
-        <x:v>0.005541299104094372</x:v>
+        <x:v>0.7966002400071364</x:v>
       </x:c>
       <x:c r="I23" s="46" t="n">
-        <x:v>0.05725878409359503</x:v>
+        <x:v>0.5535011059778423</x:v>
       </x:c>
       <x:c r="J23" s="43" t="n">
-        <x:v>0.01145062917390009</x:v>
-      </x:c>
-      <x:c r="K23" s="49" t="n">
-        <x:v>68.06131773570849</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" s="49"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="37" t="str">
-        <x:v>2.1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="B24" s="37" t="str">
-        <x:v>CDR-SB scale at 18 months</x:v>
+        <x:v>ADAS-Cog 24 months mean difference</x:v>
       </x:c>
       <x:c r="C24" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D24" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E24" s="40" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F24" s="43" t="n">
-        <x:v>-0.1236070445068449</x:v>
+        <x:v>-1.405503778337532</x:v>
       </x:c>
       <x:c r="G24" s="43" t="n">
-        <x:v>-0.2431373516407464</x:v>
+        <x:v>-5.245306413837063</x:v>
       </x:c>
       <x:c r="H24" s="43" t="n">
-        <x:v>-0.004076737372943479</x:v>
+        <x:v>2.434298857161997</x:v>
       </x:c>
       <x:c r="I24" s="46" t="n">
-        <x:v>0.04422331763822816</x:v>
+        <x:v>0.4731172993008963</x:v>
       </x:c>
       <x:c r="J24" s="43" t="n">
-        <x:v>0.00992017602479526</x:v>
+        <x:v>5.423950000000001</x:v>
       </x:c>
       <x:c r="K24" s="49" t="n">
-        <x:v>67.0327253844976</x:v>
+        <x:v>68.82792226332252</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="37" t="str">
-        <x:v>2.1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="B25" s="37" t="str">
-        <x:v>CDR-SB scale at 18 months</x:v>
+        <x:v>ADAS-Cog 24 months mean difference</x:v>
       </x:c>
       <x:c r="C25" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D25" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E25" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F25" s="43" t="n">
-        <x:v>-0.2383329171312891</x:v>
+        <x:v>-1.405503778337532</x:v>
       </x:c>
       <x:c r="G25" s="43" t="n">
-        <x:v>-0.3368502033469807</x:v>
+        <x:v>-5.245306413837063</x:v>
       </x:c>
       <x:c r="H25" s="43" t="n">
-        <x:v>-0.1398156309155975</x:v>
+        <x:v>2.434298857161997</x:v>
       </x:c>
       <x:c r="I25" s="46" t="n">
-        <x:v>0.000002120967868202937</x:v>
+        <x:v>0.4731172993008963</x:v>
       </x:c>
       <x:c r="J25" s="43" t="n">
-        <x:v>0.002334869061340162</x:v>
+        <x:v>5.423950000000001</x:v>
       </x:c>
       <x:c r="K25" s="49" t="n">
-        <x:v>45.86408424331176</x:v>
+        <x:v>68.82792226332252</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="37" t="str">
-        <x:v>2.1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="B26" s="37" t="str">
-        <x:v>CDR-SB scale at 18 months</x:v>
+        <x:v>ADAS-Cog 24 months mean difference</x:v>
       </x:c>
       <x:c r="C26" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D26" s="37" t="str">
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E26" s="40" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F26" s="43" t="n">
-        <x:v>-0.1408487094294537</x:v>
+        <x:v>-3.71</x:v>
       </x:c>
       <x:c r="G26" s="43" t="n">
-        <x:v>-0.322576224049347</x:v>
+        <x:v>-7.492730490162304</x:v>
       </x:c>
       <x:c r="H26" s="43" t="n">
-        <x:v>0.04087880519043971</x:v>
+        <x:v>0.07273049016230448</x:v>
       </x:c>
       <x:c r="I26" s="46" t="n">
-        <x:v>0.0977734175044781</x:v>
+        <x:v>0.05457056124297725</x:v>
       </x:c>
       <x:c r="J26" s="43" t="n">
-        <x:v>0.01505180879040255</x:v>
-      </x:c>
-      <x:c r="K26" s="49" t="n">
-        <x:v>75.84510866614151</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26" s="49"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="37" t="str">
@@ -2549,36 +2549,36 @@
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D27" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E27" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F27" s="43" t="n">
-        <x:v>-0.1773237574850486</x:v>
+        <x:v>-0.1368236744489688</x:v>
       </x:c>
       <x:c r="G27" s="43" t="n">
-        <x:v>-0.3801162793058889</x:v>
+        <x:v>-0.279188648002032</x:v>
       </x:c>
       <x:c r="H27" s="43" t="n">
-        <x:v>0.02546876433579176</x:v>
+        <x:v>0.005541299104094372</x:v>
       </x:c>
       <x:c r="I27" s="46" t="n">
-        <x:v>0.06883215469400818</x:v>
+        <x:v>0.05725878409359503</x:v>
       </x:c>
       <x:c r="J27" s="43" t="n">
-        <x:v>0.01105171366056151</x:v>
+        <x:v>0.01145062917390009</x:v>
       </x:c>
       <x:c r="K27" s="49" t="n">
-        <x:v>72.93959835639485</x:v>
+        <x:v>68.06131773570849</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="37" t="str">
-        <x:v>2.2</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="B28" s="37" t="str">
-        <x:v>CDR-SB scale at 24 months</x:v>
+        <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C28" s="37" t="str">
         <x:v>SMD</x:v>
@@ -2587,157 +2587,159 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E28" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F28" s="43" t="n">
-        <x:v>0.03154549881786915</x:v>
+        <x:v>-0.1236070445068449</x:v>
       </x:c>
       <x:c r="G28" s="43" t="n">
-        <x:v>-0.2347697798861706</x:v>
+        <x:v>-0.2431373516407464</x:v>
       </x:c>
       <x:c r="H28" s="43" t="n">
-        <x:v>0.2978607775219089</x:v>
+        <x:v>-0.004076737372943479</x:v>
       </x:c>
       <x:c r="I28" s="46" t="n">
-        <x:v>0.8164129089891102</x:v>
+        <x:v>0.04422331763822816</x:v>
       </x:c>
       <x:c r="J28" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.00992017602479526</x:v>
       </x:c>
       <x:c r="K28" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>67.0327253844976</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="37" t="str">
-        <x:v>2.2</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="B29" s="37" t="str">
-        <x:v>CDR-SB scale at 24 months</x:v>
+        <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C29" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D29" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E29" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F29" s="43" t="n">
-        <x:v>-0.125093</x:v>
+        <x:v>-0.2383329171312891</x:v>
       </x:c>
       <x:c r="G29" s="43" t="n">
-        <x:v>-0.7243813877328897</x:v>
+        <x:v>-0.3368502033469807</x:v>
       </x:c>
       <x:c r="H29" s="43" t="n">
-        <x:v>0.4741953877328897</x:v>
+        <x:v>-0.1398156309155975</x:v>
       </x:c>
       <x:c r="I29" s="46" t="n">
-        <x:v>0.6824553839373367</x:v>
+        <x:v>0.000002120967868202937</x:v>
       </x:c>
       <x:c r="J29" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="49"/>
+        <x:v>0.002334869061340162</x:v>
+      </x:c>
+      <x:c r="K29" s="49" t="n">
+        <x:v>45.86408424331176</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="37" t="str">
-        <x:v>2.3</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="B30" s="37" t="str">
-        <x:v>CDR-SB scale above 24 months</x:v>
+        <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C30" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D30" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E30" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F30" s="43" t="n">
-        <x:v>-0.07010296517035747</x:v>
+        <x:v>-0.1408487094294537</x:v>
       </x:c>
       <x:c r="G30" s="43" t="n">
-        <x:v>-0.1587119765097488</x:v>
+        <x:v>-0.322576224049347</x:v>
       </x:c>
       <x:c r="H30" s="43" t="n">
-        <x:v>0.01850604616903387</x:v>
+        <x:v>0.04087880519043971</x:v>
       </x:c>
       <x:c r="I30" s="46" t="n">
-        <x:v>0.1209917431904372</x:v>
+        <x:v>0.0977734175044781</x:v>
       </x:c>
       <x:c r="J30" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.01505180879040255</x:v>
       </x:c>
       <x:c r="K30" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>75.84510866614151</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="37" t="str">
-        <x:v>2.3</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="B31" s="37" t="str">
-        <x:v>CDR-SB scale above 24 months</x:v>
+        <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C31" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D31" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E31" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F31" s="43" t="n">
-        <x:v>-0.07010296517035747</x:v>
+        <x:v>-0.1773237574850486</x:v>
       </x:c>
       <x:c r="G31" s="43" t="n">
-        <x:v>-0.1587119765097488</x:v>
+        <x:v>-0.3801162793058889</x:v>
       </x:c>
       <x:c r="H31" s="43" t="n">
-        <x:v>0.01850604616903387</x:v>
+        <x:v>0.02546876433579176</x:v>
       </x:c>
       <x:c r="I31" s="46" t="n">
-        <x:v>0.1209917431904372</x:v>
+        <x:v>0.06883215469400818</x:v>
       </x:c>
       <x:c r="J31" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.01105171366056151</x:v>
       </x:c>
       <x:c r="K31" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>72.93959835639485</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="37" t="str">
-        <x:v>2.4</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="B32" s="37" t="str">
-        <x:v>CDR-SB 24 months mean difference</x:v>
+        <x:v>CDR-SB scale at 24 months</x:v>
       </x:c>
       <x:c r="C32" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D32" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E32" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F32" s="43" t="n">
-        <x:v>0.03187919463087242</x:v>
+        <x:v>0.03154549881786915</x:v>
       </x:c>
       <x:c r="G32" s="43" t="n">
-        <x:v>-0.6425001302343454</x:v>
+        <x:v>-0.2347697798861706</x:v>
       </x:c>
       <x:c r="H32" s="43" t="n">
-        <x:v>0.7062585194960902</x:v>
+        <x:v>0.2978607775219089</x:v>
       </x:c>
       <x:c r="I32" s="46" t="n">
-        <x:v>0.9261806438041792</x:v>
+        <x:v>0.8164129089891102</x:v>
       </x:c>
       <x:c r="J32" s="43" t="n">
         <x:v>0</x:v>
@@ -2748,78 +2750,78 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="37" t="str">
-        <x:v>2.4</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="B33" s="37" t="str">
-        <x:v>CDR-SB 24 months mean difference</x:v>
+        <x:v>CDR-SB scale at 24 months</x:v>
       </x:c>
       <x:c r="C33" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D33" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E33" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F33" s="43" t="n">
-        <x:v>-0.25</x:v>
+        <x:v>0.03154549881786915</x:v>
       </x:c>
       <x:c r="G33" s="43" t="n">
-        <x:v>-1.425978390724032</x:v>
+        <x:v>-0.2347697798861706</x:v>
       </x:c>
       <x:c r="H33" s="43" t="n">
-        <x:v>0.9259783907240324</x:v>
+        <x:v>0.2978607775219089</x:v>
       </x:c>
       <x:c r="I33" s="46" t="n">
-        <x:v>0.6769222390213793</x:v>
+        <x:v>0.8164129089891102</x:v>
       </x:c>
       <x:c r="J33" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="49"/>
+      <x:c r="K33" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="37" t="str">
-        <x:v>3.1</x:v>
+        <x:v>2.2</x:v>
       </x:c>
       <x:c r="B34" s="37" t="str">
-        <x:v>DAD total score at 18 months</x:v>
+        <x:v>CDR-SB scale at 24 months</x:v>
       </x:c>
       <x:c r="C34" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D34" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E34" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F34" s="43" t="n">
-        <x:v>0.04141224471514686</x:v>
+        <x:v>-0.125093</x:v>
       </x:c>
       <x:c r="G34" s="43" t="n">
-        <x:v>-0.1598196720713164</x:v>
+        <x:v>-0.7243813877328897</x:v>
       </x:c>
       <x:c r="H34" s="43" t="n">
-        <x:v>0.2426441615016101</x:v>
+        <x:v>0.4741953877328897</x:v>
       </x:c>
       <x:c r="I34" s="46" t="n">
-        <x:v>0.5592504435881637</x:v>
+        <x:v>0.6824553839373367</x:v>
       </x:c>
       <x:c r="J34" s="43" t="n">
-        <x:v>0.008246332150662004</x:v>
-      </x:c>
-      <x:c r="K34" s="49" t="n">
-        <x:v>47.339757601024054</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K34" s="49"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37" t="str">
-        <x:v>3.2</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="B35" s="37" t="str">
-        <x:v>ADCS-ADL score at 18 months</x:v>
+        <x:v>CDR-SB scale above 24 months</x:v>
       </x:c>
       <x:c r="C35" s="37" t="str">
         <x:v>SMD</x:v>
@@ -2831,16 +2833,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F35" s="43" t="n">
-        <x:v>0.08816284866786056</x:v>
+        <x:v>-0.07010296517035747</x:v>
       </x:c>
       <x:c r="G35" s="43" t="n">
-        <x:v>0.003686722140595511</x:v>
+        <x:v>-0.1587119765097488</x:v>
       </x:c>
       <x:c r="H35" s="43" t="n">
-        <x:v>0.1726389751951256</x:v>
+        <x:v>0.01850604616903387</x:v>
       </x:c>
       <x:c r="I35" s="46" t="n">
-        <x:v>0.04080548270414162</x:v>
+        <x:v>0.1209917431904372</x:v>
       </x:c>
       <x:c r="J35" s="43" t="n">
         <x:v>0</x:v>
@@ -2851,10 +2853,10 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37" t="str">
-        <x:v>3.2</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="B36" s="37" t="str">
-        <x:v>ADCS-ADL score at 18 months</x:v>
+        <x:v>CDR-SB scale above 24 months</x:v>
       </x:c>
       <x:c r="C36" s="37" t="str">
         <x:v>SMD</x:v>
@@ -2863,19 +2865,19 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E36" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F36" s="43" t="n">
-        <x:v>0.09178831812571328</x:v>
+        <x:v>-0.07010296517035747</x:v>
       </x:c>
       <x:c r="G36" s="43" t="n">
-        <x:v>0.0263970931581225</x:v>
+        <x:v>-0.1587119765097488</x:v>
       </x:c>
       <x:c r="H36" s="43" t="n">
-        <x:v>0.1571795430933041</x:v>
+        <x:v>0.01850604616903387</x:v>
       </x:c>
       <x:c r="I36" s="46" t="n">
-        <x:v>0.02633697419299469</x:v>
+        <x:v>0.1209917431904372</x:v>
       </x:c>
       <x:c r="J36" s="43" t="n">
         <x:v>0</x:v>
@@ -2886,81 +2888,83 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="37" t="str">
-        <x:v>3.3</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="B37" s="37" t="str">
-        <x:v>ADCS-ADL score at 24 months</x:v>
+        <x:v>CDR-SB scale above 24 months</x:v>
       </x:c>
       <x:c r="C37" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D37" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E37" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F37" s="43" t="n">
-        <x:v>0.08682091859005583</x:v>
+        <x:v>-0.07010296517035747</x:v>
       </x:c>
       <x:c r="G37" s="43" t="n">
-        <x:v>-0.5172299831097308</x:v>
+        <x:v>-0.1587119765097488</x:v>
       </x:c>
       <x:c r="H37" s="43" t="n">
-        <x:v>0.6908718202898424</x:v>
+        <x:v>0.01850604616903387</x:v>
       </x:c>
       <x:c r="I37" s="46" t="n">
-        <x:v>0.7781675439764495</x:v>
+        <x:v>0.1209917431904372</x:v>
       </x:c>
       <x:c r="J37" s="43" t="n">
-        <x:v>0.1346995454279999</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K37" s="49" t="n">
-        <x:v>67.83682538876192</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="37" t="str">
-        <x:v>3.3</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="B38" s="37" t="str">
-        <x:v>ADCS-ADL score at 24 months</x:v>
+        <x:v>CDR-SB 24 months mean difference</x:v>
       </x:c>
       <x:c r="C38" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D38" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E38" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F38" s="43" t="n">
-        <x:v>0.46747</x:v>
+        <x:v>0.03187919463087242</x:v>
       </x:c>
       <x:c r="G38" s="43" t="n">
-        <x:v>-0.1681698397541541</x:v>
+        <x:v>-0.6425001302343454</x:v>
       </x:c>
       <x:c r="H38" s="43" t="n">
-        <x:v>1.103109839754154</x:v>
+        <x:v>0.7062585194960902</x:v>
       </x:c>
       <x:c r="I38" s="46" t="n">
-        <x:v>0.1494658918971332</x:v>
+        <x:v>0.9261806438041792</x:v>
       </x:c>
       <x:c r="J38" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K38" s="49"/>
+      <x:c r="K38" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="37" t="str">
-        <x:v>3.4</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="B39" s="37" t="str">
-        <x:v>ADCS-ADL score above 24 months</x:v>
+        <x:v>CDR-SB 24 months mean difference</x:v>
       </x:c>
       <x:c r="C39" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D39" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
@@ -2969,16 +2973,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F39" s="43" t="n">
-        <x:v>0.06945122787161243</x:v>
+        <x:v>0.03187919463087242</x:v>
       </x:c>
       <x:c r="G39" s="43" t="n">
-        <x:v>-0.01885827939760293</x:v>
+        <x:v>-0.6425001302343454</x:v>
       </x:c>
       <x:c r="H39" s="43" t="n">
-        <x:v>0.1577607351408278</x:v>
+        <x:v>0.7062585194960902</x:v>
       </x:c>
       <x:c r="I39" s="46" t="n">
-        <x:v>0.1232149723966561</x:v>
+        <x:v>0.9261806438041792</x:v>
       </x:c>
       <x:c r="J39" s="43" t="n">
         <x:v>0</x:v>
@@ -2989,101 +2993,99 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="37" t="str">
-        <x:v>3.4</x:v>
+        <x:v>2.4</x:v>
       </x:c>
       <x:c r="B40" s="37" t="str">
-        <x:v>ADCS-ADL score above 24 months</x:v>
+        <x:v>CDR-SB 24 months mean difference</x:v>
       </x:c>
       <x:c r="C40" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D40" s="37" t="str">
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E40" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F40" s="43" t="n">
-        <x:v>0.06945122787161243</x:v>
+        <x:v>-0.25</x:v>
       </x:c>
       <x:c r="G40" s="43" t="n">
-        <x:v>-0.01885827939760293</x:v>
+        <x:v>-1.425978390724032</x:v>
       </x:c>
       <x:c r="H40" s="43" t="n">
-        <x:v>0.1577607351408278</x:v>
+        <x:v>0.9259783907240324</x:v>
       </x:c>
       <x:c r="I40" s="46" t="n">
-        <x:v>0.1232149723966561</x:v>
+        <x:v>0.6769222390213793</x:v>
       </x:c>
       <x:c r="J40" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K40" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K40" s="49"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="37" t="str">
-        <x:v>3.5</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="B41" s="37" t="str">
-        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
+        <x:v>DAD total score at 18 months</x:v>
       </x:c>
       <x:c r="C41" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D41" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E41" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F41" s="43" t="n">
-        <x:v>0.2253197481892245</x:v>
+        <x:v>0.04141224471514686</x:v>
       </x:c>
       <x:c r="G41" s="43" t="n">
-        <x:v>0.1157058503293755</x:v>
+        <x:v>-0.1598196720713164</x:v>
       </x:c>
       <x:c r="H41" s="43" t="n">
-        <x:v>0.3349336460490735</x:v>
+        <x:v>0.2426441615016101</x:v>
       </x:c>
       <x:c r="I41" s="46" t="n">
-        <x:v>0.007261190132686397</x:v>
+        <x:v>0.5592504435881637</x:v>
       </x:c>
       <x:c r="J41" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.008246332150662004</x:v>
       </x:c>
       <x:c r="K41" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>47.339757601024054</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="37" t="str">
-        <x:v>3.5</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="B42" s="37" t="str">
-        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
+        <x:v>ADCS-ADL score at 18 months</x:v>
       </x:c>
       <x:c r="C42" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D42" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E42" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F42" s="43" t="n">
-        <x:v>0.2253197481892245</x:v>
+        <x:v>0.08816284866786056</x:v>
       </x:c>
       <x:c r="G42" s="43" t="n">
-        <x:v>0.1157058503293755</x:v>
+        <x:v>0.003686722140595511</x:v>
       </x:c>
       <x:c r="H42" s="43" t="n">
-        <x:v>0.3349336460490735</x:v>
+        <x:v>0.1726389751951256</x:v>
       </x:c>
       <x:c r="I42" s="46" t="n">
-        <x:v>0.007261190132686397</x:v>
+        <x:v>0.04080548270414162</x:v>
       </x:c>
       <x:c r="J42" s="43" t="n">
         <x:v>0</x:v>
@@ -3094,134 +3096,136 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="37" t="str">
-        <x:v>3.5</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="B43" s="37" t="str">
-        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
+        <x:v>ADCS-ADL score at 18 months</x:v>
       </x:c>
       <x:c r="C43" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D43" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E43" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F43" s="43" t="n">
-        <x:v>0.246614</x:v>
+        <x:v>0.09178831812571328</x:v>
       </x:c>
       <x:c r="G43" s="43" t="n">
-        <x:v>0.1475868196811138</x:v>
+        <x:v>0.0263970931581225</x:v>
       </x:c>
       <x:c r="H43" s="43" t="n">
-        <x:v>0.3456411803188862</x:v>
+        <x:v>0.1571795430933041</x:v>
       </x:c>
       <x:c r="I43" s="46" t="n">
-        <x:v>0.000001055336161928896</x:v>
+        <x:v>0.02633697419299469</x:v>
       </x:c>
       <x:c r="J43" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K43" s="49"/>
+      <x:c r="K43" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="37" t="str">
-        <x:v>3.5</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="B44" s="37" t="str">
-        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
+        <x:v>ADCS-ADL score at 24 months</x:v>
       </x:c>
       <x:c r="C44" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D44" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E44" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F44" s="43" t="n">
-        <x:v>0.2243525052917481</x:v>
+        <x:v>0.08682091859005583</x:v>
       </x:c>
       <x:c r="G44" s="43" t="n">
-        <x:v>0.05231967903803061</x:v>
+        <x:v>-0.5172299831097308</x:v>
       </x:c>
       <x:c r="H44" s="43" t="n">
-        <x:v>0.3963853315454655</x:v>
+        <x:v>0.6908718202898424</x:v>
       </x:c>
       <x:c r="I44" s="46" t="n">
-        <x:v>0.03032334779759622</x:v>
+        <x:v>0.7781675439764495</x:v>
       </x:c>
       <x:c r="J44" s="43" t="n">
-        <x:v>0.000002346847165024738</x:v>
+        <x:v>0.1346995454279999</x:v>
       </x:c>
       <x:c r="K44" s="49" t="n">
-        <x:v>0.04763907167056925</x:v>
+        <x:v>67.83682538876192</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="37" t="str">
-        <x:v>3.5</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="B45" s="37" t="str">
-        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
+        <x:v>ADCS-ADL score at 24 months</x:v>
       </x:c>
       <x:c r="C45" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D45" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E45" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F45" s="43" t="n">
-        <x:v>0.2243525052917481</x:v>
+        <x:v>0.08682091859005583</x:v>
       </x:c>
       <x:c r="G45" s="43" t="n">
-        <x:v>0.05231967903803061</x:v>
+        <x:v>-0.5172299831097308</x:v>
       </x:c>
       <x:c r="H45" s="43" t="n">
-        <x:v>0.3963853315454655</x:v>
+        <x:v>0.6908718202898424</x:v>
       </x:c>
       <x:c r="I45" s="46" t="n">
-        <x:v>0.03032334779759622</x:v>
+        <x:v>0.7781675439764495</x:v>
       </x:c>
       <x:c r="J45" s="43" t="n">
-        <x:v>0.000002346847165024738</x:v>
+        <x:v>0.1346995454279999</x:v>
       </x:c>
       <x:c r="K45" s="49" t="n">
-        <x:v>0.04763907167056925</x:v>
+        <x:v>67.83682538876192</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.3</x:v>
       </x:c>
       <x:c r="B46" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score at 24 months</x:v>
       </x:c>
       <x:c r="C46" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D46" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E46" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F46" s="43" t="n">
-        <x:v>0.2086615152924401</x:v>
+        <x:v>0.46747</x:v>
       </x:c>
       <x:c r="G46" s="43" t="n">
-        <x:v>0.09740270301361312</x:v>
+        <x:v>-0.1681698397541541</x:v>
       </x:c>
       <x:c r="H46" s="43" t="n">
-        <x:v>0.3199203275712671</x:v>
+        <x:v>1.103109839754154</x:v>
       </x:c>
       <x:c r="I46" s="46" t="n">
-        <x:v>0.0002370725624849406</x:v>
+        <x:v>0.1494658918971332</x:v>
       </x:c>
       <x:c r="J46" s="43" t="n">
         <x:v>0</x:v>
@@ -3230,76 +3234,80 @@
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="B47" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score above 24 months</x:v>
       </x:c>
       <x:c r="C47" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D47" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E47" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F47" s="43" t="n">
-        <x:v>0.2086615152924401</x:v>
+        <x:v>0.06945122787161243</x:v>
       </x:c>
       <x:c r="G47" s="43" t="n">
-        <x:v>0.09740270301361312</x:v>
+        <x:v>-0.01885827939760293</x:v>
       </x:c>
       <x:c r="H47" s="43" t="n">
-        <x:v>0.3199203275712671</x:v>
+        <x:v>0.1577607351408278</x:v>
       </x:c>
       <x:c r="I47" s="46" t="n">
-        <x:v>0.0002370725624849406</x:v>
+        <x:v>0.1232149723966561</x:v>
       </x:c>
       <x:c r="J47" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K47" s="49"/>
+      <x:c r="K47" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="B48" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score above 24 months</x:v>
       </x:c>
       <x:c r="C48" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D48" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E48" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F48" s="43" t="n">
-        <x:v>0.2086615152924401</x:v>
+        <x:v>0.06945122787161243</x:v>
       </x:c>
       <x:c r="G48" s="43" t="n">
-        <x:v>0.09740270301361312</x:v>
+        <x:v>-0.01885827939760293</x:v>
       </x:c>
       <x:c r="H48" s="43" t="n">
-        <x:v>0.3199203275712671</x:v>
+        <x:v>0.1577607351408278</x:v>
       </x:c>
       <x:c r="I48" s="46" t="n">
-        <x:v>0.0002370725624849406</x:v>
+        <x:v>0.1232149723966561</x:v>
       </x:c>
       <x:c r="J48" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K48" s="49"/>
+      <x:c r="K48" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="B49" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score above 24 months</x:v>
       </x:c>
       <x:c r="C49" s="37" t="str">
         <x:v>SMD</x:v>
@@ -3308,120 +3316,124 @@
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E49" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F49" s="43" t="n">
-        <x:v>0.2086615152924401</x:v>
+        <x:v>0.06945122787161243</x:v>
       </x:c>
       <x:c r="G49" s="43" t="n">
-        <x:v>0.09740270301361312</x:v>
+        <x:v>-0.01885827939760293</x:v>
       </x:c>
       <x:c r="H49" s="43" t="n">
-        <x:v>0.3199203275712671</x:v>
+        <x:v>0.1577607351408278</x:v>
       </x:c>
       <x:c r="I49" s="46" t="n">
-        <x:v>0.0002370725624849406</x:v>
+        <x:v>0.1232149723966561</x:v>
       </x:c>
       <x:c r="J49" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K49" s="49"/>
+      <x:c r="K49" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="B50" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
       </x:c>
       <x:c r="C50" s="37" t="str">
         <x:v>SMD</x:v>
       </x:c>
       <x:c r="D50" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E50" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F50" s="43" t="n">
-        <x:v>0.2086615152924401</x:v>
+        <x:v>0.2253197481892245</x:v>
       </x:c>
       <x:c r="G50" s="43" t="n">
-        <x:v>0.09740270301361312</x:v>
+        <x:v>0.1157058503293755</x:v>
       </x:c>
       <x:c r="H50" s="43" t="n">
-        <x:v>0.3199203275712671</x:v>
+        <x:v>0.3349336460490735</x:v>
       </x:c>
       <x:c r="I50" s="46" t="n">
-        <x:v>0.0002370725624849406</x:v>
+        <x:v>0.007261190132686397</x:v>
       </x:c>
       <x:c r="J50" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K50" s="49"/>
+      <x:c r="K50" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="37" t="str">
-        <x:v>3.7</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="B51" s="37" t="str">
-        <x:v>ADCS-ADL 24 months mean difference</x:v>
+        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
       </x:c>
       <x:c r="C51" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D51" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E51" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F51" s="43" t="n">
-        <x:v>0.6478059440559435</x:v>
+        <x:v>0.2253197481892245</x:v>
       </x:c>
       <x:c r="G51" s="43" t="n">
-        <x:v>-4.919750116189824</x:v>
+        <x:v>0.1157058503293755</x:v>
       </x:c>
       <x:c r="H51" s="43" t="n">
-        <x:v>6.215362004301711</x:v>
+        <x:v>0.3349336460490735</x:v>
       </x:c>
       <x:c r="I51" s="46" t="n">
-        <x:v>0.8196080459316482</x:v>
+        <x:v>0.007261190132686397</x:v>
       </x:c>
       <x:c r="J51" s="43" t="n">
-        <x:v>11.602949999999998</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K51" s="49" t="n">
-        <x:v>70.92614553278888</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="37" t="str">
-        <x:v>3.7</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="B52" s="37" t="str">
-        <x:v>ADCS-ADL 24 months mean difference</x:v>
+        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
       </x:c>
       <x:c r="C52" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D52" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E52" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F52" s="43" t="n">
-        <x:v>3.84</x:v>
+        <x:v>0.246614</x:v>
       </x:c>
       <x:c r="G52" s="43" t="n">
-        <x:v>-1.216707080113341</x:v>
+        <x:v>0.1475868196811138</x:v>
       </x:c>
       <x:c r="H52" s="43" t="n">
-        <x:v>8.896707080113341</x:v>
+        <x:v>0.3456411803188862</x:v>
       </x:c>
       <x:c r="I52" s="46" t="n">
-        <x:v>0.136652792031436</x:v>
+        <x:v>0.000001055336161928896</x:v>
       </x:c>
       <x:c r="J52" s="43" t="n">
         <x:v>0</x:v>
@@ -3430,101 +3442,101 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="37" t="str">
-        <x:v>3.8</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="B53" s="37" t="str">
-        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
+        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
       </x:c>
       <x:c r="C53" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D53" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E53" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F53" s="43" t="n">
-        <x:v>1.89589160244829</x:v>
+        <x:v>0.2243525052917481</x:v>
       </x:c>
       <x:c r="G53" s="43" t="n">
-        <x:v>1.401633901320093</x:v>
+        <x:v>0.05231967903803061</x:v>
       </x:c>
       <x:c r="H53" s="43" t="n">
-        <x:v>2.390149303576488</x:v>
+        <x:v>0.3963853315454655</x:v>
       </x:c>
       <x:c r="I53" s="46" t="n">
-        <x:v>0.001183624489583718</x:v>
+        <x:v>0.03032334779759622</x:v>
       </x:c>
       <x:c r="J53" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.000002346847165024738</x:v>
       </x:c>
       <x:c r="K53" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>0.04763907167056925</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="37" t="str">
-        <x:v>3.8</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="B54" s="37" t="str">
-        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
+        <x:v>ADCS-ADL-MCI score at 18 months</x:v>
       </x:c>
       <x:c r="C54" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D54" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E54" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F54" s="43" t="n">
-        <x:v>1.89589160244829</x:v>
+        <x:v>0.2243525052917481</x:v>
       </x:c>
       <x:c r="G54" s="43" t="n">
-        <x:v>1.401633901320093</x:v>
+        <x:v>0.05231967903803061</x:v>
       </x:c>
       <x:c r="H54" s="43" t="n">
-        <x:v>2.390149303576488</x:v>
+        <x:v>0.3963853315454655</x:v>
       </x:c>
       <x:c r="I54" s="46" t="n">
-        <x:v>0.001183624489583718</x:v>
+        <x:v>0.03032334779759622</x:v>
       </x:c>
       <x:c r="J54" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.000002346847165024738</x:v>
       </x:c>
       <x:c r="K54" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>0.04763907167056925</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="37" t="str">
-        <x:v>3.8</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B55" s="37" t="str">
-        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C55" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D55" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E55" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F55" s="43" t="n">
-        <x:v>2</x:v>
+        <x:v>0.2086615152924401</x:v>
       </x:c>
       <x:c r="G55" s="43" t="n">
-        <x:v>1.196414766338578</x:v>
+        <x:v>0.09740270301361312</x:v>
       </x:c>
       <x:c r="H55" s="43" t="n">
-        <x:v>2.803585233661422</x:v>
+        <x:v>0.3199203275712671</x:v>
       </x:c>
       <x:c r="I55" s="46" t="n">
-        <x:v>0.000001071404313668343</x:v>
+        <x:v>0.0002370725624849406</x:v>
       </x:c>
       <x:c r="J55" s="43" t="n">
         <x:v>0</x:v>
@@ -3533,324 +3545,318 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="37" t="str">
-        <x:v>3.8</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B56" s="37" t="str">
-        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C56" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D56" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E56" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F56" s="43" t="n">
-        <x:v>1.878575390824981</x:v>
+        <x:v>0.2086615152924401</x:v>
       </x:c>
       <x:c r="G56" s="43" t="n">
-        <x:v>1.390837406015276</x:v>
+        <x:v>0.09740270301361312</x:v>
       </x:c>
       <x:c r="H56" s="43" t="n">
-        <x:v>2.366313375634687</x:v>
+        <x:v>0.3199203275712671</x:v>
       </x:c>
       <x:c r="I56" s="46" t="n">
-        <x:v>0.003621422276681959</x:v>
+        <x:v>0.0002370725624849406</x:v>
       </x:c>
       <x:c r="J56" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K56" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K56" s="49"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="37" t="str">
-        <x:v>3.8</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B57" s="37" t="str">
-        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C57" s="37" t="str">
-        <x:v>MD</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D57" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E57" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F57" s="43" t="n">
-        <x:v>1.878575390824981</x:v>
+        <x:v>0.2086615152924401</x:v>
       </x:c>
       <x:c r="G57" s="43" t="n">
-        <x:v>1.390837406015276</x:v>
+        <x:v>0.09740270301361312</x:v>
       </x:c>
       <x:c r="H57" s="43" t="n">
-        <x:v>2.366313375634687</x:v>
+        <x:v>0.3199203275712671</x:v>
       </x:c>
       <x:c r="I57" s="46" t="n">
-        <x:v>0.003621422276681959</x:v>
+        <x:v>0.0002370725624849406</x:v>
       </x:c>
       <x:c r="J57" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K57" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K57" s="49"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="37" t="str">
-        <x:v>4.1</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B58" s="37" t="str">
-        <x:v>Any ARIA at 18 months</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C58" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D58" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E58" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F58" s="43" t="n">
-        <x:v>2.396697026053299</x:v>
+        <x:v>0.2086615152924401</x:v>
       </x:c>
       <x:c r="G58" s="43" t="n">
-        <x:v>2.074870925771339</x:v>
+        <x:v>0.09740270301361312</x:v>
       </x:c>
       <x:c r="H58" s="43" t="n">
-        <x:v>2.768440466993059</x:v>
+        <x:v>0.3199203275712671</x:v>
       </x:c>
       <x:c r="I58" s="46" t="n">
-        <x:v>1.481404164582036e-32</x:v>
+        <x:v>0.0002370725624849406</x:v>
       </x:c>
       <x:c r="J58" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K58" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K58" s="49"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="37" t="str">
-        <x:v>4.1</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B59" s="37" t="str">
-        <x:v>Any ARIA at 18 months</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C59" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D59" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E59" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F59" s="43" t="n">
-        <x:v>2.396697026053299</x:v>
+        <x:v>0.2086615152924401</x:v>
       </x:c>
       <x:c r="G59" s="43" t="n">
-        <x:v>2.074870925771339</x:v>
+        <x:v>0.09740270301361312</x:v>
       </x:c>
       <x:c r="H59" s="43" t="n">
-        <x:v>2.768440466993059</x:v>
+        <x:v>0.3199203275712671</x:v>
       </x:c>
       <x:c r="I59" s="46" t="n">
-        <x:v>1.481404164582036e-32</x:v>
+        <x:v>0.0002370725624849406</x:v>
       </x:c>
       <x:c r="J59" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K59" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K59" s="49"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="37" t="str">
-        <x:v>4.1</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="B60" s="37" t="str">
-        <x:v>Any ARIA at 18 months</x:v>
+        <x:v>ADCS-ADL 24 months mean difference</x:v>
       </x:c>
       <x:c r="C60" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D60" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E60" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F60" s="43" t="n">
-        <x:v>2.396697026053299</x:v>
+        <x:v>0.6478059440559435</x:v>
       </x:c>
       <x:c r="G60" s="43" t="n">
-        <x:v>2.074870925771339</x:v>
+        <x:v>-4.919750116189824</x:v>
       </x:c>
       <x:c r="H60" s="43" t="n">
-        <x:v>2.768440466993059</x:v>
+        <x:v>6.215362004301711</x:v>
       </x:c>
       <x:c r="I60" s="46" t="n">
-        <x:v>1.481404164582036e-32</x:v>
+        <x:v>0.8196080459316482</x:v>
       </x:c>
       <x:c r="J60" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>11.602949999999998</x:v>
       </x:c>
       <x:c r="K60" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>70.92614553278888</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="37" t="str">
-        <x:v>4.1</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="B61" s="37" t="str">
-        <x:v>Any ARIA at 18 months</x:v>
+        <x:v>ADCS-ADL 24 months mean difference</x:v>
       </x:c>
       <x:c r="C61" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D61" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E61" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F61" s="43" t="n">
-        <x:v>2.396697026053299</x:v>
+        <x:v>0.6478059440559435</x:v>
       </x:c>
       <x:c r="G61" s="43" t="n">
-        <x:v>2.074870925771339</x:v>
+        <x:v>-4.919750116189824</x:v>
       </x:c>
       <x:c r="H61" s="43" t="n">
-        <x:v>2.768440466993059</x:v>
+        <x:v>6.215362004301711</x:v>
       </x:c>
       <x:c r="I61" s="46" t="n">
-        <x:v>1.481404164582036e-32</x:v>
+        <x:v>0.8196080459316482</x:v>
       </x:c>
       <x:c r="J61" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>11.602949999999998</x:v>
       </x:c>
       <x:c r="K61" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>70.92614553278888</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="37" t="str">
-        <x:v>4.1</x:v>
+        <x:v>3.7</x:v>
       </x:c>
       <x:c r="B62" s="37" t="str">
-        <x:v>Any ARIA at 18 months</x:v>
+        <x:v>ADCS-ADL 24 months mean difference</x:v>
       </x:c>
       <x:c r="C62" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D62" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E62" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F62" s="43" t="n">
-        <x:v>2.396697026053299</x:v>
+        <x:v>3.84</x:v>
       </x:c>
       <x:c r="G62" s="43" t="n">
-        <x:v>2.074870925771339</x:v>
+        <x:v>-1.216707080113341</x:v>
       </x:c>
       <x:c r="H62" s="43" t="n">
-        <x:v>2.768440466993059</x:v>
+        <x:v>8.896707080113341</x:v>
       </x:c>
       <x:c r="I62" s="46" t="n">
-        <x:v>1.481404164582036e-32</x:v>
+        <x:v>0.136652792031436</x:v>
       </x:c>
       <x:c r="J62" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K62" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K62" s="49"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="37" t="str">
-        <x:v>4.10</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="B63" s="37" t="str">
-        <x:v>Symptomatic ARIA H at 18 months</x:v>
+        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
       </x:c>
       <x:c r="C63" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D63" s="37" t="str">
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E63" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F63" s="43" t="n">
-        <x:v>2.996659242761693</x:v>
+        <x:v>1.89589160244829</x:v>
       </x:c>
       <x:c r="G63" s="43" t="n">
-        <x:v>0.6064524420319729</x:v>
+        <x:v>1.401633901320093</x:v>
       </x:c>
       <x:c r="H63" s="43" t="n">
-        <x:v>14.807371518104377</x:v>
+        <x:v>2.390149303576488</x:v>
       </x:c>
       <x:c r="I63" s="46" t="n">
-        <x:v>0.1781711995829671</x:v>
+        <x:v>0.001183624489583718</x:v>
       </x:c>
       <x:c r="J63" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K63" s="49"/>
+      <x:c r="K63" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="37" t="str">
-        <x:v>4.10</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="B64" s="37" t="str">
-        <x:v>Symptomatic ARIA H at 18 months</x:v>
+        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
       </x:c>
       <x:c r="C64" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D64" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E64" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F64" s="43" t="n">
-        <x:v>2.996659242761693</x:v>
+        <x:v>1.89589160244829</x:v>
       </x:c>
       <x:c r="G64" s="43" t="n">
-        <x:v>0.6064524420319729</x:v>
+        <x:v>1.401633901320093</x:v>
       </x:c>
       <x:c r="H64" s="43" t="n">
-        <x:v>14.807371518104377</x:v>
+        <x:v>2.390149303576488</x:v>
       </x:c>
       <x:c r="I64" s="46" t="n">
-        <x:v>0.1781711995829671</x:v>
+        <x:v>0.001183624489583718</x:v>
       </x:c>
       <x:c r="J64" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K64" s="49"/>
+      <x:c r="K64" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="37" t="str">
-        <x:v>4.10</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="B65" s="37" t="str">
-        <x:v>Symptomatic ARIA H at 18 months</x:v>
+        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
       </x:c>
       <x:c r="C65" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D65" s="37" t="str">
         <x:v>Currently active agents: lecanemab + donanemab</x:v>
@@ -3859,16 +3865,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F65" s="43" t="n">
-        <x:v>2.996659242761693</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G65" s="43" t="n">
-        <x:v>0.6064524420319729</x:v>
+        <x:v>1.196414766338578</x:v>
       </x:c>
       <x:c r="H65" s="43" t="n">
-        <x:v>14.807371518104377</x:v>
+        <x:v>2.803585233661422</x:v>
       </x:c>
       <x:c r="I65" s="46" t="n">
-        <x:v>0.1781711995829671</x:v>
+        <x:v>0.000001071404313668343</x:v>
       </x:c>
       <x:c r="J65" s="43" t="n">
         <x:v>0</x:v>
@@ -3877,76 +3883,80 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="37" t="str">
-        <x:v>4.10</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="B66" s="37" t="str">
-        <x:v>Symptomatic ARIA H at 18 months</x:v>
+        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
       </x:c>
       <x:c r="C66" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D66" s="37" t="str">
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E66" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F66" s="43" t="n">
-        <x:v>2.996659242761693</x:v>
+        <x:v>1.878575390824981</x:v>
       </x:c>
       <x:c r="G66" s="43" t="n">
-        <x:v>0.6064524420319729</x:v>
+        <x:v>1.390837406015276</x:v>
       </x:c>
       <x:c r="H66" s="43" t="n">
-        <x:v>14.807371518104377</x:v>
+        <x:v>2.366313375634687</x:v>
       </x:c>
       <x:c r="I66" s="46" t="n">
-        <x:v>0.1781711995829671</x:v>
+        <x:v>0.003621422276681959</x:v>
       </x:c>
       <x:c r="J66" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K66" s="49"/>
+      <x:c r="K66" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="37" t="str">
-        <x:v>4.10</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="B67" s="37" t="str">
-        <x:v>Symptomatic ARIA H at 18 months</x:v>
+        <x:v>ADCS-ADL-MCI 18 months mean difference</x:v>
       </x:c>
       <x:c r="C67" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>MD</x:v>
       </x:c>
       <x:c r="D67" s="37" t="str">
         <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E67" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F67" s="43" t="n">
-        <x:v>2.996659242761693</x:v>
+        <x:v>1.878575390824981</x:v>
       </x:c>
       <x:c r="G67" s="43" t="n">
-        <x:v>0.6064524420319729</x:v>
+        <x:v>1.390837406015276</x:v>
       </x:c>
       <x:c r="H67" s="43" t="n">
-        <x:v>14.807371518104377</x:v>
+        <x:v>2.366313375634687</x:v>
       </x:c>
       <x:c r="I67" s="46" t="n">
-        <x:v>0.1781711995829671</x:v>
+        <x:v>0.003621422276681959</x:v>
       </x:c>
       <x:c r="J67" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K67" s="49"/>
+      <x:c r="K67" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="37" t="str">
-        <x:v>4.2</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="B68" s="37" t="str">
-        <x:v>Any ARIA E at 18 months</x:v>
+        <x:v>Any ARIA at 18 months</x:v>
       </x:c>
       <x:c r="C68" s="37" t="str">
         <x:v>RR</x:v>
@@ -3955,33 +3965,33 @@
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E68" s="40" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F68" s="43" t="n">
-        <x:v>10.815852087805371</x:v>
+        <x:v>2.396697026053299</x:v>
       </x:c>
       <x:c r="G68" s="43" t="n">
-        <x:v>7.385208138975721</x:v>
+        <x:v>2.074870925771339</x:v>
       </x:c>
       <x:c r="H68" s="43" t="n">
-        <x:v>15.840129916975977</x:v>
+        <x:v>2.768440466993059</x:v>
       </x:c>
       <x:c r="I68" s="46" t="n">
-        <x:v>0.00001714310594345255</x:v>
+        <x:v>1.481404164582036e-32</x:v>
       </x:c>
       <x:c r="J68" s="43" t="n">
-        <x:v>0.000002252954523501713</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K68" s="49" t="n">
-        <x:v>0.002041916513044677</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="37" t="str">
-        <x:v>4.2</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="B69" s="37" t="str">
-        <x:v>Any ARIA E at 18 months</x:v>
+        <x:v>Any ARIA at 18 months</x:v>
       </x:c>
       <x:c r="C69" s="37" t="str">
         <x:v>RR</x:v>
@@ -3990,33 +4000,33 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E69" s="40" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F69" s="43" t="n">
-        <x:v>10.021567099643446</x:v>
+        <x:v>2.396697026053299</x:v>
       </x:c>
       <x:c r="G69" s="43" t="n">
-        <x:v>6.528842377875721</x:v>
+        <x:v>2.074870925771339</x:v>
       </x:c>
       <x:c r="H69" s="43" t="n">
-        <x:v>15.382789370591807</x:v>
+        <x:v>2.768440466993059</x:v>
       </x:c>
       <x:c r="I69" s="46" t="n">
-        <x:v>2.958196663618207e-7</x:v>
+        <x:v>1.481404164582036e-32</x:v>
       </x:c>
       <x:c r="J69" s="43" t="n">
-        <x:v>0.0542301570159683</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K69" s="49" t="n">
-        <x:v>25.234597256918885</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="37" t="str">
-        <x:v>4.2</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="B70" s="37" t="str">
-        <x:v>Any ARIA E at 18 months</x:v>
+        <x:v>Any ARIA at 18 months</x:v>
       </x:c>
       <x:c r="C70" s="37" t="str">
         <x:v>RR</x:v>
@@ -4028,30 +4038,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F70" s="43" t="n">
-        <x:v>9.534152467053653</x:v>
+        <x:v>2.396697026053299</x:v>
       </x:c>
       <x:c r="G70" s="43" t="n">
-        <x:v>6.21064491112134</x:v>
+        <x:v>2.074870925771339</x:v>
       </x:c>
       <x:c r="H70" s="43" t="n">
-        <x:v>14.636171374449603</x:v>
+        <x:v>2.768440466993059</x:v>
       </x:c>
       <x:c r="I70" s="46" t="n">
-        <x:v>6.280012932944558e-25</x:v>
+        <x:v>1.481404164582036e-32</x:v>
       </x:c>
       <x:c r="J70" s="43" t="n">
-        <x:v>0.03054202110557434</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K70" s="49" t="n">
-        <x:v>31.733789919128956</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="37" t="str">
-        <x:v>4.2</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="B71" s="37" t="str">
-        <x:v>Any ARIA E at 18 months</x:v>
+        <x:v>Any ARIA at 18 months</x:v>
       </x:c>
       <x:c r="C71" s="37" t="str">
         <x:v>RR</x:v>
@@ -4060,33 +4070,33 @@
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E71" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F71" s="43" t="n">
-        <x:v>11.126627376704237</x:v>
+        <x:v>2.396697026053299</x:v>
       </x:c>
       <x:c r="G71" s="43" t="n">
-        <x:v>7.300100747407355</x:v>
+        <x:v>2.074870925771339</x:v>
       </x:c>
       <x:c r="H71" s="43" t="n">
-        <x:v>16.95892167296358</x:v>
+        <x:v>2.768440466993059</x:v>
       </x:c>
       <x:c r="I71" s="46" t="n">
-        <x:v>0.0003622734079252079</x:v>
+        <x:v>1.481404164582036e-32</x:v>
       </x:c>
       <x:c r="J71" s="43" t="n">
-        <x:v>0.000005486735187794456</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K71" s="49" t="n">
-        <x:v>0.008088407276469487</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="37" t="str">
-        <x:v>4.2</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="B72" s="37" t="str">
-        <x:v>Any ARIA E at 18 months</x:v>
+        <x:v>Any ARIA at 18 months</x:v>
       </x:c>
       <x:c r="C72" s="37" t="str">
         <x:v>RR</x:v>
@@ -4095,33 +4105,33 @@
         <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E72" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F72" s="43" t="n">
-        <x:v>11.126627376704237</x:v>
+        <x:v>2.396697026053299</x:v>
       </x:c>
       <x:c r="G72" s="43" t="n">
-        <x:v>7.300100747407355</x:v>
+        <x:v>2.074870925771339</x:v>
       </x:c>
       <x:c r="H72" s="43" t="n">
-        <x:v>16.95892167296358</x:v>
+        <x:v>2.768440466993059</x:v>
       </x:c>
       <x:c r="I72" s="46" t="n">
-        <x:v>0.0003622734079252079</x:v>
+        <x:v>1.481404164582036e-32</x:v>
       </x:c>
       <x:c r="J72" s="43" t="n">
-        <x:v>0.000005486735187794456</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K72" s="49" t="n">
-        <x:v>0.008088407276469487</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="37" t="str">
-        <x:v>4.3</x:v>
+        <x:v>4.10</x:v>
       </x:c>
       <x:c r="B73" s="37" t="str">
-        <x:v>Any ARIA E at 24 months</x:v>
+        <x:v>Symptomatic ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C73" s="37" t="str">
         <x:v>RR</x:v>
@@ -4130,33 +4140,31 @@
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E73" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F73" s="43" t="n">
-        <x:v>15.127830776127716</x:v>
+        <x:v>2.996659242761693</x:v>
       </x:c>
       <x:c r="G73" s="43" t="n">
-        <x:v>4.256872390820871</x:v>
+        <x:v>0.6064524420319729</x:v>
       </x:c>
       <x:c r="H73" s="43" t="n">
-        <x:v>53.760423846538316</x:v>
+        <x:v>14.807371518104377</x:v>
       </x:c>
       <x:c r="I73" s="46" t="n">
-        <x:v>0.00002681196792810722</x:v>
+        <x:v>0.1781711995829671</x:v>
       </x:c>
       <x:c r="J73" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K73" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K73" s="49"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="37" t="str">
-        <x:v>4.3</x:v>
+        <x:v>4.10</x:v>
       </x:c>
       <x:c r="B74" s="37" t="str">
-        <x:v>Any ARIA E at 24 months</x:v>
+        <x:v>Symptomatic ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C74" s="37" t="str">
         <x:v>RR</x:v>
@@ -4165,138 +4173,130 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E74" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F74" s="43" t="n">
-        <x:v>7.494102135327068</x:v>
+        <x:v>2.996659242761693</x:v>
       </x:c>
       <x:c r="G74" s="43" t="n">
-        <x:v>1.592420420316632</x:v>
+        <x:v>0.6064524420319729</x:v>
       </x:c>
       <x:c r="H74" s="43" t="n">
-        <x:v>35.268052392562716</x:v>
+        <x:v>14.807371518104377</x:v>
       </x:c>
       <x:c r="I74" s="46" t="n">
-        <x:v>0.0256130998592611</x:v>
+        <x:v>0.1781711995829671</x:v>
       </x:c>
       <x:c r="J74" s="43" t="n">
-        <x:v>0.1144766506372429</x:v>
-      </x:c>
-      <x:c r="K74" s="49" t="n">
-        <x:v>11.83959632683999</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K74" s="49"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="37" t="str">
-        <x:v>4.3</x:v>
+        <x:v>4.10</x:v>
       </x:c>
       <x:c r="B75" s="37" t="str">
-        <x:v>Any ARIA E at 24 months</x:v>
+        <x:v>Symptomatic ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C75" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D75" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E75" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F75" s="43" t="n">
-        <x:v>9.777363730769789</x:v>
+        <x:v>2.996659242761693</x:v>
       </x:c>
       <x:c r="G75" s="43" t="n">
-        <x:v>3.427602081862421</x:v>
+        <x:v>0.6064524420319729</x:v>
       </x:c>
       <x:c r="H75" s="43" t="n">
-        <x:v>27.89029742677396</x:v>
+        <x:v>14.807371518104377</x:v>
       </x:c>
       <x:c r="I75" s="46" t="n">
-        <x:v>0.00002014078171150615</x:v>
+        <x:v>0.1781711995829671</x:v>
       </x:c>
       <x:c r="J75" s="43" t="n">
-        <x:v>0.131015468808171</x:v>
-      </x:c>
-      <x:c r="K75" s="49" t="n">
-        <x:v>22.55874703163387</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="49"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="37" t="str">
-        <x:v>4.4</x:v>
+        <x:v>4.10</x:v>
       </x:c>
       <x:c r="B76" s="37" t="str">
-        <x:v>Any ARIA E above 24 months</x:v>
+        <x:v>Symptomatic ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C76" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D76" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E76" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F76" s="43" t="n">
-        <x:v>9.349943398952874</x:v>
+        <x:v>2.996659242761693</x:v>
       </x:c>
       <x:c r="G76" s="43" t="n">
-        <x:v>4.51505569501341</x:v>
+        <x:v>0.6064524420319729</x:v>
       </x:c>
       <x:c r="H76" s="43" t="n">
-        <x:v>19.362206685550703</x:v>
+        <x:v>14.807371518104377</x:v>
       </x:c>
       <x:c r="I76" s="46" t="n">
-        <x:v>1.75948832335529e-9</x:v>
+        <x:v>0.1781711995829671</x:v>
       </x:c>
       <x:c r="J76" s="43" t="n">
-        <x:v>0.1860143735694401</x:v>
-      </x:c>
-      <x:c r="K76" s="49" t="n">
-        <x:v>66.3692954998454</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76" s="49"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="37" t="str">
-        <x:v>4.4</x:v>
+        <x:v>4.10</x:v>
       </x:c>
       <x:c r="B77" s="37" t="str">
-        <x:v>Any ARIA E above 24 months</x:v>
+        <x:v>Symptomatic ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C77" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D77" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E77" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F77" s="43" t="n">
-        <x:v>9.349943398952874</x:v>
+        <x:v>2.996659242761693</x:v>
       </x:c>
       <x:c r="G77" s="43" t="n">
-        <x:v>4.51505569501341</x:v>
+        <x:v>0.6064524420319729</x:v>
       </x:c>
       <x:c r="H77" s="43" t="n">
-        <x:v>19.362206685550703</x:v>
+        <x:v>14.807371518104377</x:v>
       </x:c>
       <x:c r="I77" s="46" t="n">
-        <x:v>1.75948832335529e-9</x:v>
+        <x:v>0.1781711995829671</x:v>
       </x:c>
       <x:c r="J77" s="43" t="n">
-        <x:v>0.1860143735694401</x:v>
-      </x:c>
-      <x:c r="K77" s="49" t="n">
-        <x:v>66.3692954998454</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K77" s="49"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="37" t="str">
-        <x:v>4.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="B78" s="37" t="str">
-        <x:v>Symptomatic ARIA E at 18 months</x:v>
+        <x:v>Any ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C78" s="37" t="str">
         <x:v>RR</x:v>
@@ -4305,33 +4305,33 @@
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E78" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F78" s="43" t="n">
-        <x:v>52.4903527709673</x:v>
+        <x:v>10.815852087805371</x:v>
       </x:c>
       <x:c r="G78" s="43" t="n">
-        <x:v>10.44821029093028</x:v>
+        <x:v>7.385208138975721</x:v>
       </x:c>
       <x:c r="H78" s="43" t="n">
-        <x:v>263.7042189332959</x:v>
+        <x:v>15.840129916975977</x:v>
       </x:c>
       <x:c r="I78" s="46" t="n">
-        <x:v>0.000001516827684669414</x:v>
+        <x:v>0.00001714310594345255</x:v>
       </x:c>
       <x:c r="J78" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.000002252954523501713</x:v>
       </x:c>
       <x:c r="K78" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>0.002041916513044677</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="37" t="str">
-        <x:v>4.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="B79" s="37" t="str">
-        <x:v>Symptomatic ARIA E at 18 months</x:v>
+        <x:v>Any ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C79" s="37" t="str">
         <x:v>RR</x:v>
@@ -4340,33 +4340,33 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E79" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F79" s="43" t="n">
-        <x:v>52.4903527709673</x:v>
+        <x:v>10.021567099643446</x:v>
       </x:c>
       <x:c r="G79" s="43" t="n">
-        <x:v>10.44821029093028</x:v>
+        <x:v>6.528842377875721</x:v>
       </x:c>
       <x:c r="H79" s="43" t="n">
-        <x:v>263.7042189332959</x:v>
+        <x:v>15.382789370591807</x:v>
       </x:c>
       <x:c r="I79" s="46" t="n">
-        <x:v>0.000001516827684669414</x:v>
+        <x:v>2.958196663618207e-7</x:v>
       </x:c>
       <x:c r="J79" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0542301570159683</x:v>
       </x:c>
       <x:c r="K79" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>25.234597256918885</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="37" t="str">
-        <x:v>4.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="B80" s="37" t="str">
-        <x:v>Symptomatic ARIA E at 18 months</x:v>
+        <x:v>Any ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C80" s="37" t="str">
         <x:v>RR</x:v>
@@ -4378,30 +4378,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F80" s="43" t="n">
-        <x:v>52.4903527709673</x:v>
+        <x:v>9.534152467053653</x:v>
       </x:c>
       <x:c r="G80" s="43" t="n">
-        <x:v>10.44821029093028</x:v>
+        <x:v>6.21064491112134</x:v>
       </x:c>
       <x:c r="H80" s="43" t="n">
-        <x:v>263.7042189332959</x:v>
+        <x:v>14.636171374449603</x:v>
       </x:c>
       <x:c r="I80" s="46" t="n">
-        <x:v>0.000001516827684669414</x:v>
+        <x:v>6.280012932944558e-25</x:v>
       </x:c>
       <x:c r="J80" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.03054202110557434</x:v>
       </x:c>
       <x:c r="K80" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>31.733789919128956</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="37" t="str">
-        <x:v>4.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="B81" s="37" t="str">
-        <x:v>Symptomatic ARIA E at 18 months</x:v>
+        <x:v>Any ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C81" s="37" t="str">
         <x:v>RR</x:v>
@@ -4410,33 +4410,33 @@
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E81" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F81" s="43" t="n">
-        <x:v>52.4903527709673</x:v>
+        <x:v>11.126627376704237</x:v>
       </x:c>
       <x:c r="G81" s="43" t="n">
-        <x:v>10.44821029093028</x:v>
+        <x:v>7.300100747407355</x:v>
       </x:c>
       <x:c r="H81" s="43" t="n">
-        <x:v>263.7042189332959</x:v>
+        <x:v>16.95892167296358</x:v>
       </x:c>
       <x:c r="I81" s="46" t="n">
-        <x:v>0.000001516827684669414</x:v>
+        <x:v>0.0003622734079252079</x:v>
       </x:c>
       <x:c r="J81" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.000005486735187794456</x:v>
       </x:c>
       <x:c r="K81" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>0.008088407276469487</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="37" t="str">
-        <x:v>4.5</x:v>
+        <x:v>4.2</x:v>
       </x:c>
       <x:c r="B82" s="37" t="str">
-        <x:v>Symptomatic ARIA E at 18 months</x:v>
+        <x:v>Any ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C82" s="37" t="str">
         <x:v>RR</x:v>
@@ -4445,208 +4445,208 @@
         <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E82" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F82" s="43" t="n">
-        <x:v>52.4903527709673</x:v>
+        <x:v>11.126627376704237</x:v>
       </x:c>
       <x:c r="G82" s="43" t="n">
-        <x:v>10.44821029093028</x:v>
+        <x:v>7.300100747407355</x:v>
       </x:c>
       <x:c r="H82" s="43" t="n">
-        <x:v>263.7042189332959</x:v>
+        <x:v>16.95892167296358</x:v>
       </x:c>
       <x:c r="I82" s="46" t="n">
-        <x:v>0.000001516827684669414</x:v>
+        <x:v>0.0003622734079252079</x:v>
       </x:c>
       <x:c r="J82" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.000005486735187794456</x:v>
       </x:c>
       <x:c r="K82" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>0.008088407276469487</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="37" t="str">
-        <x:v>4.6</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="B83" s="37" t="str">
-        <x:v>Symptomatic ARIA E above 24 months</x:v>
+        <x:v>Any ARIA E at 24 months</x:v>
       </x:c>
       <x:c r="C83" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D83" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E83" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F83" s="43" t="n">
-        <x:v>15.546661816944196</x:v>
+        <x:v>7.494102135327068</x:v>
       </x:c>
       <x:c r="G83" s="43" t="n">
-        <x:v>4.331361582881384</x:v>
+        <x:v>1.592420420316632</x:v>
       </x:c>
       <x:c r="H83" s="43" t="n">
-        <x:v>55.80201260630923</x:v>
+        <x:v>35.268052392562716</x:v>
       </x:c>
       <x:c r="I83" s="46" t="n">
-        <x:v>0.00002574921926643576</x:v>
+        <x:v>0.0256130998592611</x:v>
       </x:c>
       <x:c r="J83" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1144766506372429</x:v>
       </x:c>
       <x:c r="K83" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>11.83959632683999</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="37" t="str">
-        <x:v>4.6</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="B84" s="37" t="str">
-        <x:v>Symptomatic ARIA E above 24 months</x:v>
+        <x:v>Any ARIA E at 24 months</x:v>
       </x:c>
       <x:c r="C84" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D84" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E84" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F84" s="43" t="n">
-        <x:v>15.546661816944196</x:v>
+        <x:v>7.494102135327068</x:v>
       </x:c>
       <x:c r="G84" s="43" t="n">
-        <x:v>4.331361582881384</x:v>
+        <x:v>1.592420420316632</x:v>
       </x:c>
       <x:c r="H84" s="43" t="n">
-        <x:v>55.80201260630923</x:v>
+        <x:v>35.268052392562716</x:v>
       </x:c>
       <x:c r="I84" s="46" t="n">
-        <x:v>0.00002574921926643576</x:v>
+        <x:v>0.0256130998592611</x:v>
       </x:c>
       <x:c r="J84" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1144766506372429</x:v>
       </x:c>
       <x:c r="K84" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>11.83959632683999</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="37" t="str">
-        <x:v>4.7</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="B85" s="37" t="str">
-        <x:v>Any ARIA H at 18 months</x:v>
+        <x:v>Any ARIA E at 24 months</x:v>
       </x:c>
       <x:c r="C85" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D85" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E85" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F85" s="43" t="n">
-        <x:v>1.647567809136657</x:v>
+        <x:v>9.777363730769789</x:v>
       </x:c>
       <x:c r="G85" s="43" t="n">
-        <x:v>0.4720670649431771</x:v>
+        <x:v>3.427602081862421</x:v>
       </x:c>
       <x:c r="H85" s="43" t="n">
-        <x:v>5.750199256180067</x:v>
+        <x:v>27.89029742677396</x:v>
       </x:c>
       <x:c r="I85" s="46" t="n">
-        <x:v>0.2278005662462623</x:v>
+        <x:v>0.00002014078171150615</x:v>
       </x:c>
       <x:c r="J85" s="43" t="n">
-        <x:v>0.1956923723665924</x:v>
+        <x:v>0.131015468808171</x:v>
       </x:c>
       <x:c r="K85" s="49" t="n">
-        <x:v>90.00231897534974</x:v>
+        <x:v>22.55874703163387</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="37" t="str">
-        <x:v>4.7</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="B86" s="37" t="str">
-        <x:v>Any ARIA H at 18 months</x:v>
+        <x:v>Any ARIA E above 24 months</x:v>
       </x:c>
       <x:c r="C86" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D86" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E86" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F86" s="43" t="n">
-        <x:v>1.647567809136657</x:v>
+        <x:v>9.349943398952874</x:v>
       </x:c>
       <x:c r="G86" s="43" t="n">
-        <x:v>0.4720670649431771</x:v>
+        <x:v>4.51505569501341</x:v>
       </x:c>
       <x:c r="H86" s="43" t="n">
-        <x:v>5.750199256180067</x:v>
+        <x:v>19.362206685550703</x:v>
       </x:c>
       <x:c r="I86" s="46" t="n">
-        <x:v>0.2278005662462623</x:v>
+        <x:v>1.75948832335529e-9</x:v>
       </x:c>
       <x:c r="J86" s="43" t="n">
-        <x:v>0.1956923723665924</x:v>
+        <x:v>0.1860143735694401</x:v>
       </x:c>
       <x:c r="K86" s="49" t="n">
-        <x:v>90.00231897534974</x:v>
+        <x:v>66.3692954998454</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="37" t="str">
-        <x:v>4.7</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="B87" s="37" t="str">
-        <x:v>Any ARIA H at 18 months</x:v>
+        <x:v>Any ARIA E above 24 months</x:v>
       </x:c>
       <x:c r="C87" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D87" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E87" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F87" s="43" t="n">
-        <x:v>2.138161182743667</x:v>
+        <x:v>9.349943398952874</x:v>
       </x:c>
       <x:c r="G87" s="43" t="n">
-        <x:v>1.783838716365453</x:v>
+        <x:v>4.51505569501341</x:v>
       </x:c>
       <x:c r="H87" s="43" t="n">
-        <x:v>2.562862438991481</x:v>
+        <x:v>19.362206685550703</x:v>
       </x:c>
       <x:c r="I87" s="46" t="n">
-        <x:v>2.018307569553946e-16</x:v>
+        <x:v>1.75948832335529e-9</x:v>
       </x:c>
       <x:c r="J87" s="43" t="n">
-        <x:v>0.004539150272811225</x:v>
+        <x:v>0.1860143735694401</x:v>
       </x:c>
       <x:c r="K87" s="49" t="n">
-        <x:v>25.597636053393874</x:v>
+        <x:v>66.3692954998454</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="37" t="str">
-        <x:v>4.7</x:v>
+        <x:v>4.4</x:v>
       </x:c>
       <x:c r="B88" s="37" t="str">
-        <x:v>Any ARIA H at 18 months</x:v>
+        <x:v>Any ARIA E above 24 months</x:v>
       </x:c>
       <x:c r="C88" s="37" t="str">
         <x:v>RR</x:v>
@@ -4658,86 +4658,86 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F88" s="43" t="n">
-        <x:v>2.138161182743667</x:v>
+        <x:v>9.349943398952874</x:v>
       </x:c>
       <x:c r="G88" s="43" t="n">
-        <x:v>1.783838716365453</x:v>
+        <x:v>4.51505569501341</x:v>
       </x:c>
       <x:c r="H88" s="43" t="n">
-        <x:v>2.562862438991481</x:v>
+        <x:v>19.362206685550703</x:v>
       </x:c>
       <x:c r="I88" s="46" t="n">
-        <x:v>2.018307569553946e-16</x:v>
+        <x:v>1.75948832335529e-9</x:v>
       </x:c>
       <x:c r="J88" s="43" t="n">
-        <x:v>0.004539150272811225</x:v>
+        <x:v>0.1860143735694401</x:v>
       </x:c>
       <x:c r="K88" s="49" t="n">
-        <x:v>25.597636053393874</x:v>
+        <x:v>66.3692954998454</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="37" t="str">
-        <x:v>4.7</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="B89" s="37" t="str">
-        <x:v>Any ARIA H at 18 months</x:v>
+        <x:v>Symptomatic ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C89" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D89" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E89" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F89" s="43" t="n">
-        <x:v>2.138161182743667</x:v>
+        <x:v>52.4903527709673</x:v>
       </x:c>
       <x:c r="G89" s="43" t="n">
-        <x:v>1.783838716365453</x:v>
+        <x:v>10.44821029093028</x:v>
       </x:c>
       <x:c r="H89" s="43" t="n">
-        <x:v>2.562862438991481</x:v>
+        <x:v>263.7042189332959</x:v>
       </x:c>
       <x:c r="I89" s="46" t="n">
-        <x:v>2.018307569553946e-16</x:v>
+        <x:v>0.000001516827684669414</x:v>
       </x:c>
       <x:c r="J89" s="43" t="n">
-        <x:v>0.004539150272811225</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K89" s="49" t="n">
-        <x:v>25.597636053393874</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="37" t="str">
-        <x:v>4.8</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="B90" s="37" t="str">
-        <x:v>Any ARIA H at 24 months</x:v>
+        <x:v>Symptomatic ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C90" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D90" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E90" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F90" s="43" t="n">
-        <x:v>1.244115745899325</x:v>
+        <x:v>52.4903527709673</x:v>
       </x:c>
       <x:c r="G90" s="43" t="n">
-        <x:v>0.8249067146999729</x:v>
+        <x:v>10.44821029093028</x:v>
       </x:c>
       <x:c r="H90" s="43" t="n">
-        <x:v>1.876362456035521</x:v>
+        <x:v>263.7042189332959</x:v>
       </x:c>
       <x:c r="I90" s="46" t="n">
-        <x:v>0.297482797745303</x:v>
+        <x:v>0.000001516827684669414</x:v>
       </x:c>
       <x:c r="J90" s="43" t="n">
         <x:v>0</x:v>
@@ -4748,31 +4748,31 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="37" t="str">
-        <x:v>4.8</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="B91" s="37" t="str">
-        <x:v>Any ARIA H at 24 months</x:v>
+        <x:v>Symptomatic ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C91" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D91" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E91" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F91" s="43" t="n">
-        <x:v>1.274817128129933</x:v>
+        <x:v>52.4903527709673</x:v>
       </x:c>
       <x:c r="G91" s="43" t="n">
-        <x:v>1.076618490467784</x:v>
+        <x:v>10.44821029093028</x:v>
       </x:c>
       <x:c r="H91" s="43" t="n">
-        <x:v>1.509502878282657</x:v>
+        <x:v>263.7042189332959</x:v>
       </x:c>
       <x:c r="I91" s="46" t="n">
-        <x:v>0.01962356765593944</x:v>
+        <x:v>0.000001516827684669414</x:v>
       </x:c>
       <x:c r="J91" s="43" t="n">
         <x:v>0</x:v>
@@ -4783,10 +4783,10 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="37" t="str">
-        <x:v>4.8</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="B92" s="37" t="str">
-        <x:v>Any ARIA H at 24 months</x:v>
+        <x:v>Symptomatic ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C92" s="37" t="str">
         <x:v>RR</x:v>
@@ -4798,16 +4798,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F92" s="43" t="n">
-        <x:v>1.277548679197549</x:v>
+        <x:v>52.4903527709673</x:v>
       </x:c>
       <x:c r="G92" s="43" t="n">
-        <x:v>0.8784500876611419</x:v>
+        <x:v>10.44821029093028</x:v>
       </x:c>
       <x:c r="H92" s="43" t="n">
-        <x:v>1.857966264269972</x:v>
+        <x:v>263.7042189332959</x:v>
       </x:c>
       <x:c r="I92" s="46" t="n">
-        <x:v>0.1999172862096003</x:v>
+        <x:v>0.000001516827684669414</x:v>
       </x:c>
       <x:c r="J92" s="43" t="n">
         <x:v>0</x:v>
@@ -4818,31 +4818,31 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="37" t="str">
-        <x:v>4.9</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="B93" s="37" t="str">
-        <x:v>Any ARIA H above 24 months</x:v>
+        <x:v>Symptomatic ARIA E at 18 months</x:v>
       </x:c>
       <x:c r="C93" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D93" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E93" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F93" s="43" t="n">
-        <x:v>1.86453837103413</x:v>
+        <x:v>52.4903527709673</x:v>
       </x:c>
       <x:c r="G93" s="43" t="n">
-        <x:v>1.518623298927227</x:v>
+        <x:v>10.44821029093028</x:v>
       </x:c>
       <x:c r="H93" s="43" t="n">
-        <x:v>2.289246674612755</x:v>
+        <x:v>263.7042189332959</x:v>
       </x:c>
       <x:c r="I93" s="46" t="n">
-        <x:v>2.674353802685868e-9</x:v>
+        <x:v>0.000001516827684669414</x:v>
       </x:c>
       <x:c r="J93" s="43" t="n">
         <x:v>0</x:v>
@@ -4853,31 +4853,31 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="37" t="str">
-        <x:v>4.9</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="B94" s="37" t="str">
-        <x:v>Any ARIA H above 24 months</x:v>
+        <x:v>Symptomatic ARIA E above 24 months</x:v>
       </x:c>
       <x:c r="C94" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D94" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E94" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F94" s="43" t="n">
-        <x:v>1.86453837103413</x:v>
+        <x:v>15.546661816944196</x:v>
       </x:c>
       <x:c r="G94" s="43" t="n">
-        <x:v>1.518623298927227</x:v>
+        <x:v>4.331361582881384</x:v>
       </x:c>
       <x:c r="H94" s="43" t="n">
-        <x:v>2.289246674612755</x:v>
+        <x:v>55.80201260630923</x:v>
       </x:c>
       <x:c r="I94" s="46" t="n">
-        <x:v>2.674353802685868e-9</x:v>
+        <x:v>0.00002574921926643576</x:v>
       </x:c>
       <x:c r="J94" s="43" t="n">
         <x:v>0</x:v>
@@ -4888,276 +4888,276 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="37" t="str">
-        <x:v>5.1</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="B95" s="37" t="str">
-        <x:v>SAE at 18 months</x:v>
+        <x:v>Symptomatic ARIA E above 24 months</x:v>
       </x:c>
       <x:c r="C95" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D95" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E95" s="40" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F95" s="43" t="n">
-        <x:v>0.9956185618334735</x:v>
+        <x:v>15.546661816944196</x:v>
       </x:c>
       <x:c r="G95" s="43" t="n">
-        <x:v>0.8414225662462191</x:v>
+        <x:v>4.331361582881384</x:v>
       </x:c>
       <x:c r="H95" s="43" t="n">
-        <x:v>1.178071946762229</x:v>
+        <x:v>55.80201260630923</x:v>
       </x:c>
       <x:c r="I95" s="46" t="n">
-        <x:v>0.9491176378529872</x:v>
+        <x:v>0.00002574921926643576</x:v>
       </x:c>
       <x:c r="J95" s="43" t="n">
-        <x:v>0.009258353416222937</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K95" s="49" t="n">
-        <x:v>35.17113632728306</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="37" t="str">
-        <x:v>5.1</x:v>
+        <x:v>4.6</x:v>
       </x:c>
       <x:c r="B96" s="37" t="str">
-        <x:v>SAE at 18 months</x:v>
+        <x:v>Symptomatic ARIA E above 24 months</x:v>
       </x:c>
       <x:c r="C96" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D96" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E96" s="40" t="n">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F96" s="43" t="n">
-        <x:v>1.041125919875473</x:v>
+        <x:v>15.546661816944196</x:v>
       </x:c>
       <x:c r="G96" s="43" t="n">
-        <x:v>0.9197385260982465</x:v>
+        <x:v>4.331361582881384</x:v>
       </x:c>
       <x:c r="H96" s="43" t="n">
-        <x:v>1.178534061887023</x:v>
+        <x:v>55.80201260630923</x:v>
       </x:c>
       <x:c r="I96" s="46" t="n">
-        <x:v>0.4749065574334275</x:v>
+        <x:v>0.00002574921926643576</x:v>
       </x:c>
       <x:c r="J96" s="43" t="n">
-        <x:v>0.0102221600342942</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K96" s="49" t="n">
-        <x:v>39.37245648976633</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="37" t="str">
-        <x:v>5.1</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="B97" s="37" t="str">
-        <x:v>SAE at 18 months</x:v>
+        <x:v>Any ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C97" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D97" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E97" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F97" s="43" t="n">
-        <x:v>1.159659887354469</x:v>
+        <x:v>1.647567809136657</x:v>
       </x:c>
       <x:c r="G97" s="43" t="n">
-        <x:v>0.9879731907852446</x:v>
+        <x:v>0.4720670649431771</x:v>
       </x:c>
       <x:c r="H97" s="43" t="n">
-        <x:v>1.361181727279584</x:v>
+        <x:v>5.750199256180067</x:v>
       </x:c>
       <x:c r="I97" s="46" t="n">
-        <x:v>0.06999319831470525</x:v>
+        <x:v>0.2278005662462623</x:v>
       </x:c>
       <x:c r="J97" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1956923723665924</x:v>
       </x:c>
       <x:c r="K97" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>90.00231897534974</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="37" t="str">
-        <x:v>5.1</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="B98" s="37" t="str">
-        <x:v>SAE at 18 months</x:v>
+        <x:v>Any ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C98" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D98" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E98" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F98" s="43" t="n">
-        <x:v>1.081077600545671</x:v>
+        <x:v>1.647567809136657</x:v>
       </x:c>
       <x:c r="G98" s="43" t="n">
-        <x:v>0.8826545261065875</x:v>
+        <x:v>0.4720670649431771</x:v>
       </x:c>
       <x:c r="H98" s="43" t="n">
-        <x:v>1.324106707475776</x:v>
+        <x:v>5.750199256180067</x:v>
       </x:c>
       <x:c r="I98" s="46" t="n">
-        <x:v>0.3084795546311091</x:v>
+        <x:v>0.2278005662462623</x:v>
       </x:c>
       <x:c r="J98" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.1956923723665924</x:v>
       </x:c>
       <x:c r="K98" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>90.00231897534974</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="37" t="str">
-        <x:v>5.1</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="B99" s="37" t="str">
-        <x:v>SAE at 18 months</x:v>
+        <x:v>Any ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C99" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D99" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E99" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F99" s="43" t="n">
-        <x:v>1.081077600545671</x:v>
+        <x:v>2.138161182743667</x:v>
       </x:c>
       <x:c r="G99" s="43" t="n">
-        <x:v>0.8826545261065875</x:v>
+        <x:v>1.783838716365453</x:v>
       </x:c>
       <x:c r="H99" s="43" t="n">
-        <x:v>1.324106707475776</x:v>
+        <x:v>2.562862438991481</x:v>
       </x:c>
       <x:c r="I99" s="46" t="n">
-        <x:v>0.3084795546311091</x:v>
+        <x:v>2.018307569553946e-16</x:v>
       </x:c>
       <x:c r="J99" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.004539150272811225</x:v>
       </x:c>
       <x:c r="K99" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>25.597636053393874</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="37" t="str">
-        <x:v>5.2</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="B100" s="37" t="str">
-        <x:v>SAE at 24 months</x:v>
+        <x:v>Any ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C100" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D100" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E100" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F100" s="43" t="n">
-        <x:v>1.024149632169375</x:v>
+        <x:v>2.138161182743667</x:v>
       </x:c>
       <x:c r="G100" s="43" t="n">
-        <x:v>0.6835671163054562</x:v>
+        <x:v>1.783838716365453</x:v>
       </x:c>
       <x:c r="H100" s="43" t="n">
-        <x:v>1.534424995078269</x:v>
+        <x:v>2.562862438991481</x:v>
       </x:c>
       <x:c r="I100" s="46" t="n">
-        <x:v>0.9079036200489142</x:v>
+        <x:v>2.018307569553946e-16</x:v>
       </x:c>
       <x:c r="J100" s="43" t="n">
-        <x:v>0.04254067415344355</x:v>
+        <x:v>0.004539150272811225</x:v>
       </x:c>
       <x:c r="K100" s="49" t="n">
-        <x:v>49.053340759619104</x:v>
+        <x:v>25.597636053393874</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="37" t="str">
-        <x:v>5.2</x:v>
+        <x:v>4.7</x:v>
       </x:c>
       <x:c r="B101" s="37" t="str">
-        <x:v>SAE at 24 months</x:v>
+        <x:v>Any ARIA H at 18 months</x:v>
       </x:c>
       <x:c r="C101" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D101" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E101" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F101" s="43" t="n">
-        <x:v>1.03100110180081</x:v>
+        <x:v>2.138161182743667</x:v>
       </x:c>
       <x:c r="G101" s="43" t="n">
-        <x:v>0.7922103769561633</x:v>
+        <x:v>1.783838716365453</x:v>
       </x:c>
       <x:c r="H101" s="43" t="n">
-        <x:v>1.341768932639596</x:v>
+        <x:v>2.562862438991481</x:v>
       </x:c>
       <x:c r="I101" s="46" t="n">
-        <x:v>0.7367734785731431</x:v>
+        <x:v>2.018307569553946e-16</x:v>
       </x:c>
       <x:c r="J101" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.004539150272811225</x:v>
       </x:c>
       <x:c r="K101" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>25.597636053393874</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="37" t="str">
-        <x:v>5.2</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="B102" s="37" t="str">
-        <x:v>SAE at 24 months</x:v>
+        <x:v>Any ARIA H at 24 months</x:v>
       </x:c>
       <x:c r="C102" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D102" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E102" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F102" s="43" t="n">
-        <x:v>0.9127084088364051</x:v>
+        <x:v>1.274817128129933</x:v>
       </x:c>
       <x:c r="G102" s="43" t="n">
-        <x:v>0.6799263193272598</x:v>
+        <x:v>1.076618490467784</x:v>
       </x:c>
       <x:c r="H102" s="43" t="n">
-        <x:v>1.225186635494438</x:v>
+        <x:v>1.509502878282657</x:v>
       </x:c>
       <x:c r="I102" s="46" t="n">
-        <x:v>0.5431736309083378</x:v>
+        <x:v>0.01962356765593944</x:v>
       </x:c>
       <x:c r="J102" s="43" t="n">
         <x:v>0</x:v>
@@ -5168,10 +5168,10 @@
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="37" t="str">
-        <x:v>5.3</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="B103" s="37" t="str">
-        <x:v>SAE above 24 months</x:v>
+        <x:v>Any ARIA H at 24 months</x:v>
       </x:c>
       <x:c r="C103" s="37" t="str">
         <x:v>RR</x:v>
@@ -5180,19 +5180,19 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E103" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F103" s="43" t="n">
-        <x:v>0.8237606397871372</x:v>
+        <x:v>1.274817128129933</x:v>
       </x:c>
       <x:c r="G103" s="43" t="n">
-        <x:v>0.6672245404164604</x:v>
+        <x:v>1.076618490467784</x:v>
       </x:c>
       <x:c r="H103" s="43" t="n">
-        <x:v>1.017021333236581</x:v>
+        <x:v>1.509502878282657</x:v>
       </x:c>
       <x:c r="I103" s="46" t="n">
-        <x:v>0.07138804072868461</x:v>
+        <x:v>0.01962356765593944</x:v>
       </x:c>
       <x:c r="J103" s="43" t="n">
         <x:v>0</x:v>
@@ -5203,10 +5203,10 @@
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="37" t="str">
-        <x:v>5.3</x:v>
+        <x:v>4.8</x:v>
       </x:c>
       <x:c r="B104" s="37" t="str">
-        <x:v>SAE above 24 months</x:v>
+        <x:v>Any ARIA H at 24 months</x:v>
       </x:c>
       <x:c r="C104" s="37" t="str">
         <x:v>RR</x:v>
@@ -5218,16 +5218,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F104" s="43" t="n">
-        <x:v>0.8237606397871372</x:v>
+        <x:v>1.277548679197549</x:v>
       </x:c>
       <x:c r="G104" s="43" t="n">
-        <x:v>0.6672245404164604</x:v>
+        <x:v>0.8784500876611419</x:v>
       </x:c>
       <x:c r="H104" s="43" t="n">
-        <x:v>1.017021333236581</x:v>
+        <x:v>1.857966264269972</x:v>
       </x:c>
       <x:c r="I104" s="46" t="n">
-        <x:v>0.07138804072868461</x:v>
+        <x:v>0.1999172862096003</x:v>
       </x:c>
       <x:c r="J104" s="43" t="n">
         <x:v>0</x:v>
@@ -5238,10 +5238,10 @@
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="37" t="str">
-        <x:v>6.1</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="B105" s="37" t="str">
-        <x:v>Mortality at 18 months</x:v>
+        <x:v>Any ARIA H above 24 months</x:v>
       </x:c>
       <x:c r="C105" s="37" t="str">
         <x:v>RR</x:v>
@@ -5250,33 +5250,33 @@
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E105" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F105" s="43" t="n">
-        <x:v>0.789896702758804</x:v>
+        <x:v>1.86453837103413</x:v>
       </x:c>
       <x:c r="G105" s="43" t="n">
-        <x:v>0.1978476089412052</x:v>
+        <x:v>1.518623298927227</x:v>
       </x:c>
       <x:c r="H105" s="43" t="n">
-        <x:v>3.153623156571211</x:v>
+        <x:v>2.289246674612755</x:v>
       </x:c>
       <x:c r="I105" s="46" t="n">
-        <x:v>0.6253789367213871</x:v>
+        <x:v>2.674353802685868e-9</x:v>
       </x:c>
       <x:c r="J105" s="43" t="n">
-        <x:v>0.2603136330532979</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K105" s="49" t="n">
-        <x:v>47.815282697116444</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="37" t="str">
-        <x:v>6.1</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="B106" s="37" t="str">
-        <x:v>Mortality at 18 months</x:v>
+        <x:v>Any ARIA H above 24 months</x:v>
       </x:c>
       <x:c r="C106" s="37" t="str">
         <x:v>RR</x:v>
@@ -5285,54 +5285,54 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E106" s="40" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F106" s="43" t="n">
-        <x:v>1.172699932526192</x:v>
+        <x:v>1.86453837103413</x:v>
       </x:c>
       <x:c r="G106" s="43" t="n">
-        <x:v>0.6151622791578121</x:v>
+        <x:v>1.518623298927227</x:v>
       </x:c>
       <x:c r="H106" s="43" t="n">
-        <x:v>2.235548534656072</x:v>
+        <x:v>2.289246674612755</x:v>
       </x:c>
       <x:c r="I106" s="46" t="n">
-        <x:v>0.5678400901058178</x:v>
+        <x:v>2.674353802685868e-9</x:v>
       </x:c>
       <x:c r="J106" s="43" t="n">
-        <x:v>0.1175095438551367</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K106" s="49" t="n">
-        <x:v>31.573527502497875</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="37" t="str">
-        <x:v>6.1</x:v>
+        <x:v>4.9</x:v>
       </x:c>
       <x:c r="B107" s="37" t="str">
-        <x:v>Mortality at 18 months</x:v>
+        <x:v>Any ARIA H above 24 months</x:v>
       </x:c>
       <x:c r="C107" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D107" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E107" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F107" s="43" t="n">
-        <x:v>1.312245888036337</x:v>
+        <x:v>1.86453837103413</x:v>
       </x:c>
       <x:c r="G107" s="43" t="n">
-        <x:v>0.6947137725702309</x:v>
+        <x:v>1.518623298927227</x:v>
       </x:c>
       <x:c r="H107" s="43" t="n">
-        <x:v>2.4787032280898</x:v>
+        <x:v>2.289246674612755</x:v>
       </x:c>
       <x:c r="I107" s="46" t="n">
-        <x:v>0.402351685815781</x:v>
+        <x:v>2.674353802685868e-9</x:v>
       </x:c>
       <x:c r="J107" s="43" t="n">
         <x:v>0</x:v>
@@ -5343,171 +5343,171 @@
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="37" t="str">
-        <x:v>6.1</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="B108" s="37" t="str">
-        <x:v>Mortality at 18 months</x:v>
+        <x:v>SAE at 18 months</x:v>
       </x:c>
       <x:c r="C108" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D108" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E108" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F108" s="43" t="n">
-        <x:v>1.312245888036337</x:v>
+        <x:v>0.9956185618334735</x:v>
       </x:c>
       <x:c r="G108" s="43" t="n">
-        <x:v>0.6947137725702309</x:v>
+        <x:v>0.8414225662462191</x:v>
       </x:c>
       <x:c r="H108" s="43" t="n">
-        <x:v>2.4787032280898</x:v>
+        <x:v>1.178071946762229</x:v>
       </x:c>
       <x:c r="I108" s="46" t="n">
-        <x:v>0.402351685815781</x:v>
+        <x:v>0.9491176378529872</x:v>
       </x:c>
       <x:c r="J108" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.009258353416222937</x:v>
       </x:c>
       <x:c r="K108" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>35.17113632728306</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="37" t="str">
-        <x:v>6.1</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="B109" s="37" t="str">
-        <x:v>Mortality at 18 months</x:v>
+        <x:v>SAE at 18 months</x:v>
       </x:c>
       <x:c r="C109" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D109" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E109" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F109" s="43" t="n">
-        <x:v>1.312245888036337</x:v>
+        <x:v>1.041125919875473</x:v>
       </x:c>
       <x:c r="G109" s="43" t="n">
-        <x:v>0.6947137725702309</x:v>
+        <x:v>0.9197385260982465</x:v>
       </x:c>
       <x:c r="H109" s="43" t="n">
-        <x:v>2.4787032280898</x:v>
+        <x:v>1.178534061887023</x:v>
       </x:c>
       <x:c r="I109" s="46" t="n">
-        <x:v>0.402351685815781</x:v>
+        <x:v>0.4749065574334275</x:v>
       </x:c>
       <x:c r="J109" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.0102221600342942</x:v>
       </x:c>
       <x:c r="K109" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>39.37245648976633</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="37" t="str">
-        <x:v>6.2</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="B110" s="37" t="str">
-        <x:v>Mortality at 24 months</x:v>
+        <x:v>SAE at 18 months</x:v>
       </x:c>
       <x:c r="C110" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D110" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="E110" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F110" s="43" t="n">
-        <x:v>0.777754100347947</x:v>
+        <x:v>1.159659887354469</x:v>
       </x:c>
       <x:c r="G110" s="43" t="n">
-        <x:v>0.08686227504736127</x:v>
+        <x:v>0.9879731907852446</x:v>
       </x:c>
       <x:c r="H110" s="43" t="n">
-        <x:v>6.963914314680622</x:v>
+        <x:v>1.361181727279584</x:v>
       </x:c>
       <x:c r="I110" s="46" t="n">
-        <x:v>0.8221895818095246</x:v>
+        <x:v>0.06999319831470525</x:v>
       </x:c>
       <x:c r="J110" s="43" t="n">
-        <x:v>1.27155151532886</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K110" s="49" t="n">
-        <x:v>46.37727217849845</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="37" t="str">
-        <x:v>6.2</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="B111" s="37" t="str">
-        <x:v>Mortality at 24 months</x:v>
+        <x:v>SAE at 18 months</x:v>
       </x:c>
       <x:c r="C111" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D111" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E111" s="40" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F111" s="43" t="n">
-        <x:v>1.054613984226482</x:v>
+        <x:v>1.081077600545671</x:v>
       </x:c>
       <x:c r="G111" s="43" t="n">
-        <x:v>0.2914924045683833</x:v>
+        <x:v>0.8826545261065875</x:v>
       </x:c>
       <x:c r="H111" s="43" t="n">
-        <x:v>3.815573367590551</x:v>
+        <x:v>1.324106707475776</x:v>
       </x:c>
       <x:c r="I111" s="46" t="n">
-        <x:v>0.9036308770545901</x:v>
+        <x:v>0.3084795546311091</x:v>
       </x:c>
       <x:c r="J111" s="43" t="n">
-        <x:v>0.05836114274397965</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K111" s="49" t="n">
-        <x:v>7.878428238569533</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="37" t="str">
-        <x:v>6.2</x:v>
+        <x:v>5.1</x:v>
       </x:c>
       <x:c r="B112" s="37" t="str">
-        <x:v>Mortality at 24 months</x:v>
+        <x:v>SAE at 18 months</x:v>
       </x:c>
       <x:c r="C112" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D112" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="E112" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F112" s="43" t="n">
-        <x:v>0.5891857123694396</x:v>
+        <x:v>1.081077600545671</x:v>
       </x:c>
       <x:c r="G112" s="43" t="n">
-        <x:v>0.1914827144903843</x:v>
+        <x:v>0.8826545261065875</x:v>
       </x:c>
       <x:c r="H112" s="43" t="n">
-        <x:v>1.812904128626798</x:v>
+        <x:v>1.324106707475776</x:v>
       </x:c>
       <x:c r="I112" s="46" t="n">
-        <x:v>0.3562632663369905</x:v>
+        <x:v>0.3084795546311091</x:v>
       </x:c>
       <x:c r="J112" s="43" t="n">
         <x:v>0</x:v>
@@ -5518,200 +5518,206 @@
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="37" t="str">
-        <x:v>6.3</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="B113" s="37" t="str">
-        <x:v>Mortality above 24 months</x:v>
+        <x:v>SAE at 24 months</x:v>
       </x:c>
       <x:c r="C113" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D113" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E113" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F113" s="43" t="n">
-        <x:v>0.6972000337432346</x:v>
+        <x:v>1.03100110180081</x:v>
       </x:c>
       <x:c r="G113" s="43" t="n">
-        <x:v>0.1251357066798499</x:v>
+        <x:v>0.7922103769561633</x:v>
       </x:c>
       <x:c r="H113" s="43" t="n">
-        <x:v>3.884485890947067</x:v>
+        <x:v>1.341768932639596</x:v>
       </x:c>
       <x:c r="I113" s="46" t="n">
-        <x:v>0.6806620419187537</x:v>
+        <x:v>0.7367734785731431</x:v>
       </x:c>
       <x:c r="J113" s="43" t="n">
-        <x:v>1.12734264450507</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K113" s="49" t="n">
-        <x:v>73.3779120362122</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="37" t="str">
-        <x:v>6.3</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="B114" s="37" t="str">
-        <x:v>Mortality above 24 months</x:v>
+        <x:v>SAE at 24 months</x:v>
       </x:c>
       <x:c r="C114" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D114" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E114" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F114" s="43" t="n">
-        <x:v>0.6972000337432346</x:v>
+        <x:v>1.03100110180081</x:v>
       </x:c>
       <x:c r="G114" s="43" t="n">
-        <x:v>0.1251357066798499</x:v>
+        <x:v>0.7922103769561633</x:v>
       </x:c>
       <x:c r="H114" s="43" t="n">
-        <x:v>3.884485890947067</x:v>
+        <x:v>1.341768932639596</x:v>
       </x:c>
       <x:c r="I114" s="46" t="n">
-        <x:v>0.6806620419187537</x:v>
+        <x:v>0.7367734785731431</x:v>
       </x:c>
       <x:c r="J114" s="43" t="n">
-        <x:v>1.12734264450507</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K114" s="49" t="n">
-        <x:v>73.3779120362122</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="37" t="str">
-        <x:v>7.1</x:v>
+        <x:v>5.2</x:v>
       </x:c>
       <x:c r="B115" s="37" t="str">
-        <x:v>NPI-Q score at 12 months</x:v>
+        <x:v>SAE at 24 months</x:v>
       </x:c>
       <x:c r="C115" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>RR</x:v>
       </x:c>
       <x:c r="D115" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E115" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F115" s="43" t="n">
-        <x:v>0.08604846600191733</x:v>
+        <x:v>0.9127084088364051</x:v>
       </x:c>
       <x:c r="G115" s="43" t="n">
-        <x:v>-0.1834920094196857</x:v>
+        <x:v>0.6799263193272598</x:v>
       </x:c>
       <x:c r="H115" s="43" t="n">
-        <x:v>0.3555889414235204</x:v>
+        <x:v>1.225186635494438</x:v>
       </x:c>
       <x:c r="I115" s="46" t="n">
-        <x:v>0.5315107139042438</x:v>
+        <x:v>0.5431736309083378</x:v>
       </x:c>
       <x:c r="J115" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K115" s="49"/>
+      <x:c r="K115" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="37" t="str">
-        <x:v>7.1</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="B116" s="37" t="str">
-        <x:v>NPI-Q score at 12 months</x:v>
+        <x:v>SAE above 24 months</x:v>
       </x:c>
       <x:c r="C116" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>RR</x:v>
       </x:c>
       <x:c r="D116" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E116" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F116" s="43" t="n">
-        <x:v>0.08604846600191733</x:v>
+        <x:v>0.8237606397871372</x:v>
       </x:c>
       <x:c r="G116" s="43" t="n">
-        <x:v>-0.1834920094196857</x:v>
+        <x:v>0.6672245404164604</x:v>
       </x:c>
       <x:c r="H116" s="43" t="n">
-        <x:v>0.3555889414235204</x:v>
+        <x:v>1.017021333236581</x:v>
       </x:c>
       <x:c r="I116" s="46" t="n">
-        <x:v>0.5315107139042438</x:v>
+        <x:v>0.07138804072868461</x:v>
       </x:c>
       <x:c r="J116" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K116" s="49"/>
+      <x:c r="K116" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="37" t="str">
-        <x:v>7.2</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="B117" s="37" t="str">
-        <x:v>NPI-Q score at 18 months</x:v>
+        <x:v>SAE above 24 months</x:v>
       </x:c>
       <x:c r="C117" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>RR</x:v>
       </x:c>
       <x:c r="D117" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E117" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F117" s="43" t="n">
-        <x:v>0.5168562568898105</x:v>
+        <x:v>0.8237606397871372</x:v>
       </x:c>
       <x:c r="G117" s="43" t="n">
-        <x:v>-0.9579855762756353</x:v>
+        <x:v>0.6672245404164604</x:v>
       </x:c>
       <x:c r="H117" s="43" t="n">
-        <x:v>1.991698090055256</x:v>
+        <x:v>1.017021333236581</x:v>
       </x:c>
       <x:c r="I117" s="46" t="n">
-        <x:v>0.4921667733628572</x:v>
+        <x:v>0.07138804072868461</x:v>
       </x:c>
       <x:c r="J117" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K117" s="49"/>
+      <x:c r="K117" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="37" t="str">
-        <x:v>7.2</x:v>
+        <x:v>5.3</x:v>
       </x:c>
       <x:c r="B118" s="37" t="str">
-        <x:v>NPI-Q score at 18 months</x:v>
+        <x:v>SAE above 24 months</x:v>
       </x:c>
       <x:c r="C118" s="37" t="str">
-        <x:v>SMD</x:v>
+        <x:v>RR</x:v>
       </x:c>
       <x:c r="D118" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E118" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F118" s="43" t="n">
-        <x:v>0.1191993997701558</x:v>
+        <x:v>0.8237606397871372</x:v>
       </x:c>
       <x:c r="G118" s="43" t="n">
-        <x:v>-0.1747924558477071</x:v>
+        <x:v>0.6672245404164604</x:v>
       </x:c>
       <x:c r="H118" s="43" t="n">
-        <x:v>0.4131912553880188</x:v>
+        <x:v>1.017021333236581</x:v>
       </x:c>
       <x:c r="I118" s="46" t="n">
-        <x:v>0.4268054428964087</x:v>
+        <x:v>0.07138804072868461</x:v>
       </x:c>
       <x:c r="J118" s="43" t="n">
         <x:v>0</x:v>
@@ -5722,10 +5728,10 @@
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="37" t="str">
-        <x:v>8.1</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="B119" s="37" t="str">
-        <x:v>Infusion reaction at 18 months</x:v>
+        <x:v>Mortality at 18 months</x:v>
       </x:c>
       <x:c r="C119" s="37" t="str">
         <x:v>RR</x:v>
@@ -5734,33 +5740,33 @@
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E119" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F119" s="43" t="n">
-        <x:v>3.580414000675478</x:v>
+        <x:v>0.789896702758804</x:v>
       </x:c>
       <x:c r="G119" s="43" t="n">
-        <x:v>0.06906491805724489</x:v>
+        <x:v>0.1978476089412052</x:v>
       </x:c>
       <x:c r="H119" s="43" t="n">
-        <x:v>185.6132574515989</x:v>
+        <x:v>3.153623156571211</x:v>
       </x:c>
       <x:c r="I119" s="46" t="n">
-        <x:v>0.2990275366168896</x:v>
+        <x:v>0.6253789367213871</x:v>
       </x:c>
       <x:c r="J119" s="43" t="n">
-        <x:v>2.363272780349808</x:v>
+        <x:v>0.2603136330532979</x:v>
       </x:c>
       <x:c r="K119" s="49" t="n">
-        <x:v>97.19728094012109</x:v>
+        <x:v>47.815282697116444</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="37" t="str">
-        <x:v>8.1</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="B120" s="37" t="str">
-        <x:v>Infusion reaction at 18 months</x:v>
+        <x:v>Mortality at 18 months</x:v>
       </x:c>
       <x:c r="C120" s="37" t="str">
         <x:v>RR</x:v>
@@ -5769,33 +5775,33 @@
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E120" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F120" s="43" t="n">
-        <x:v>3.580414000675478</x:v>
+        <x:v>1.172699932526192</x:v>
       </x:c>
       <x:c r="G120" s="43" t="n">
-        <x:v>0.06906491805724489</x:v>
+        <x:v>0.6151622791578121</x:v>
       </x:c>
       <x:c r="H120" s="43" t="n">
-        <x:v>185.6132574515989</x:v>
+        <x:v>2.235548534656072</x:v>
       </x:c>
       <x:c r="I120" s="46" t="n">
-        <x:v>0.2990275366168896</x:v>
+        <x:v>0.5678400901058178</x:v>
       </x:c>
       <x:c r="J120" s="43" t="n">
-        <x:v>2.363272780349808</x:v>
+        <x:v>0.1175095438551367</x:v>
       </x:c>
       <x:c r="K120" s="49" t="n">
-        <x:v>97.19728094012109</x:v>
+        <x:v>31.573527502497875</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="37" t="str">
-        <x:v>8.1</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="B121" s="37" t="str">
-        <x:v>Infusion reaction at 18 months</x:v>
+        <x:v>Mortality at 18 months</x:v>
       </x:c>
       <x:c r="C121" s="37" t="str">
         <x:v>RR</x:v>
@@ -5807,30 +5813,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F121" s="43" t="n">
-        <x:v>7.662918735750604</x:v>
+        <x:v>1.312245888036337</x:v>
       </x:c>
       <x:c r="G121" s="43" t="n">
-        <x:v>1.508711673369352</x:v>
+        <x:v>0.6947137725702309</x:v>
       </x:c>
       <x:c r="H121" s="43" t="n">
-        <x:v>38.920838611647795</x:v>
+        <x:v>2.4787032280898</x:v>
       </x:c>
       <x:c r="I121" s="46" t="n">
-        <x:v>0.0140512231959229</x:v>
+        <x:v>0.402351685815781</x:v>
       </x:c>
       <x:c r="J121" s="43" t="n">
-        <x:v>1.246610367970227</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K121" s="49" t="n">
-        <x:v>89.95729838569783</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="37" t="str">
-        <x:v>8.1</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="B122" s="37" t="str">
-        <x:v>Infusion reaction at 18 months</x:v>
+        <x:v>Mortality at 18 months</x:v>
       </x:c>
       <x:c r="C122" s="37" t="str">
         <x:v>RR</x:v>
@@ -5842,30 +5848,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F122" s="43" t="n">
-        <x:v>7.662918735750604</x:v>
+        <x:v>1.312245888036337</x:v>
       </x:c>
       <x:c r="G122" s="43" t="n">
-        <x:v>1.508711673369352</x:v>
+        <x:v>0.6947137725702309</x:v>
       </x:c>
       <x:c r="H122" s="43" t="n">
-        <x:v>38.920838611647795</x:v>
+        <x:v>2.4787032280898</x:v>
       </x:c>
       <x:c r="I122" s="46" t="n">
-        <x:v>0.0140512231959229</x:v>
+        <x:v>0.402351685815781</x:v>
       </x:c>
       <x:c r="J122" s="43" t="n">
-        <x:v>1.246610367970227</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K122" s="49" t="n">
-        <x:v>89.95729838569783</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="37" t="str">
-        <x:v>8.1</x:v>
+        <x:v>6.1</x:v>
       </x:c>
       <x:c r="B123" s="37" t="str">
-        <x:v>Infusion reaction at 18 months</x:v>
+        <x:v>Mortality at 18 months</x:v>
       </x:c>
       <x:c r="C123" s="37" t="str">
         <x:v>RR</x:v>
@@ -5877,241 +5883,243 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F123" s="43" t="n">
-        <x:v>7.662918735750604</x:v>
+        <x:v>1.312245888036337</x:v>
       </x:c>
       <x:c r="G123" s="43" t="n">
-        <x:v>1.508711673369352</x:v>
+        <x:v>0.6947137725702309</x:v>
       </x:c>
       <x:c r="H123" s="43" t="n">
-        <x:v>38.920838611647795</x:v>
+        <x:v>2.4787032280898</x:v>
       </x:c>
       <x:c r="I123" s="46" t="n">
-        <x:v>0.0140512231959229</x:v>
+        <x:v>0.402351685815781</x:v>
       </x:c>
       <x:c r="J123" s="43" t="n">
-        <x:v>1.246610367970227</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K123" s="49" t="n">
-        <x:v>89.95729838569783</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="37" t="str">
-        <x:v>8.2</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="B124" s="37" t="str">
-        <x:v>Infusion reaction at 24 months</x:v>
+        <x:v>Mortality at 24 months</x:v>
       </x:c>
       <x:c r="C124" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D124" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E124" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F124" s="43" t="n">
-        <x:v>1.149178942284472</x:v>
+        <x:v>1.054613984226482</x:v>
       </x:c>
       <x:c r="G124" s="43" t="n">
-        <x:v>0.7737788248778547</x:v>
+        <x:v>0.2914924045683833</x:v>
       </x:c>
       <x:c r="H124" s="43" t="n">
-        <x:v>1.706705067302049</x:v>
+        <x:v>3.815573367590551</x:v>
       </x:c>
       <x:c r="I124" s="46" t="n">
-        <x:v>0.4907956322652618</x:v>
+        <x:v>0.9036308770545901</x:v>
       </x:c>
       <x:c r="J124" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K124" s="49"/>
+        <x:v>0.05836114274397965</x:v>
+      </x:c>
+      <x:c r="K124" s="49" t="n">
+        <x:v>7.878428238569533</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="37" t="str">
-        <x:v>9.1</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="B125" s="37" t="str">
-        <x:v>Study discontinuation at 18 months</x:v>
+        <x:v>Mortality at 24 months</x:v>
       </x:c>
       <x:c r="C125" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D125" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E125" s="40" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F125" s="43" t="n">
-        <x:v>1.190649296916</x:v>
+        <x:v>1.054613984226482</x:v>
       </x:c>
       <x:c r="G125" s="43" t="n">
-        <x:v>0.9960323788259222</x:v>
+        <x:v>0.2914924045683833</x:v>
       </x:c>
       <x:c r="H125" s="43" t="n">
-        <x:v>1.423292835035767</x:v>
+        <x:v>3.815573367590551</x:v>
       </x:c>
       <x:c r="I125" s="46" t="n">
-        <x:v>0.05360998308781049</x:v>
+        <x:v>0.9036308770545901</x:v>
       </x:c>
       <x:c r="J125" s="43" t="n">
-        <x:v>0.01748992482403718</x:v>
+        <x:v>0.05836114274397965</x:v>
       </x:c>
       <x:c r="K125" s="49" t="n">
-        <x:v>53.97889282539534</x:v>
+        <x:v>7.878428238569533</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="37" t="str">
-        <x:v>9.1</x:v>
+        <x:v>6.2</x:v>
       </x:c>
       <x:c r="B126" s="37" t="str">
-        <x:v>Study discontinuation at 18 months</x:v>
+        <x:v>Mortality at 24 months</x:v>
       </x:c>
       <x:c r="C126" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D126" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E126" s="40" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F126" s="43" t="n">
-        <x:v>1.12069436507818</x:v>
+        <x:v>0.5891857123694396</x:v>
       </x:c>
       <x:c r="G126" s="43" t="n">
-        <x:v>1.020569085776655</x:v>
+        <x:v>0.1914827144903843</x:v>
       </x:c>
       <x:c r="H126" s="43" t="n">
-        <x:v>1.230642665373507</x:v>
+        <x:v>1.812904128626798</x:v>
       </x:c>
       <x:c r="I126" s="46" t="n">
-        <x:v>0.02182552233863456</x:v>
+        <x:v>0.3562632663369905</x:v>
       </x:c>
       <x:c r="J126" s="43" t="n">
-        <x:v>0.009762441228302521</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K126" s="49" t="n">
-        <x:v>49.554731620791856</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="37" t="str">
-        <x:v>9.1</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="B127" s="37" t="str">
-        <x:v>Study discontinuation at 18 months</x:v>
+        <x:v>Mortality above 24 months</x:v>
       </x:c>
       <x:c r="C127" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D127" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E127" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="F127" s="43" t="n">
-        <x:v>1.2932118172259</x:v>
+        <x:v>0.6972000337432346</x:v>
       </x:c>
       <x:c r="G127" s="43" t="n">
-        <x:v>1.133286353220927</x:v>
+        <x:v>0.1251357066798499</x:v>
       </x:c>
       <x:c r="H127" s="43" t="n">
-        <x:v>1.475705411487199</x:v>
+        <x:v>3.884485890947067</x:v>
       </x:c>
       <x:c r="I127" s="46" t="n">
-        <x:v>0.0001347038739540604</x:v>
+        <x:v>0.6806620419187537</x:v>
       </x:c>
       <x:c r="J127" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>1.12734264450507</x:v>
       </x:c>
       <x:c r="K127" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>73.3779120362122</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="37" t="str">
-        <x:v>9.1</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="B128" s="37" t="str">
-        <x:v>Study discontinuation at 18 months</x:v>
+        <x:v>Mortality above 24 months</x:v>
       </x:c>
       <x:c r="C128" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D128" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E128" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F128" s="43" t="n">
-        <x:v>1.283807373552714</x:v>
+        <x:v>0.6972000337432346</x:v>
       </x:c>
       <x:c r="G128" s="43" t="n">
-        <x:v>1.147356704309586</x:v>
+        <x:v>0.1251357066798499</x:v>
       </x:c>
       <x:c r="H128" s="43" t="n">
-        <x:v>1.436485590050296</x:v>
+        <x:v>3.884485890947067</x:v>
       </x:c>
       <x:c r="I128" s="46" t="n">
-        <x:v>0.005805190402274013</x:v>
+        <x:v>0.6806620419187537</x:v>
       </x:c>
       <x:c r="J128" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>1.12734264450507</x:v>
       </x:c>
       <x:c r="K128" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>73.3779120362122</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="37" t="str">
-        <x:v>9.1</x:v>
+        <x:v>6.3</x:v>
       </x:c>
       <x:c r="B129" s="37" t="str">
-        <x:v>Study discontinuation at 18 months</x:v>
+        <x:v>Mortality above 24 months</x:v>
       </x:c>
       <x:c r="C129" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
       <x:c r="D129" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="E129" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F129" s="43" t="n">
-        <x:v>1.283807373552714</x:v>
+        <x:v>0.6972000337432346</x:v>
       </x:c>
       <x:c r="G129" s="43" t="n">
-        <x:v>1.147356704309586</x:v>
+        <x:v>0.1251357066798499</x:v>
       </x:c>
       <x:c r="H129" s="43" t="n">
-        <x:v>1.436485590050296</x:v>
+        <x:v>3.884485890947067</x:v>
       </x:c>
       <x:c r="I129" s="46" t="n">
-        <x:v>0.005805190402274013</x:v>
+        <x:v>0.6806620419187537</x:v>
       </x:c>
       <x:c r="J129" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>1.12734264450507</x:v>
       </x:c>
       <x:c r="K129" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>73.3779120362122</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="37" t="str">
-        <x:v>9.2</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="B130" s="37" t="str">
-        <x:v>Study discontinuation at 24 months</x:v>
+        <x:v>NPI-Q score at 12 months</x:v>
       </x:c>
       <x:c r="C130" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D130" s="37" t="str">
         <x:v>Biomarker-confirmed</x:v>
@@ -6120,16 +6128,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F130" s="43" t="n">
-        <x:v>1.05361653272101</x:v>
+        <x:v>0.08604846600191733</x:v>
       </x:c>
       <x:c r="G130" s="43" t="n">
-        <x:v>0.7888018745680653</x:v>
+        <x:v>-0.1834920094196857</x:v>
       </x:c>
       <x:c r="H130" s="43" t="n">
-        <x:v>1.407334127636195</x:v>
+        <x:v>0.3555889414235204</x:v>
       </x:c>
       <x:c r="I130" s="46" t="n">
-        <x:v>0.7236128240599273</x:v>
+        <x:v>0.5315107139042438</x:v>
       </x:c>
       <x:c r="J130" s="43" t="n">
         <x:v>0</x:v>
@@ -6138,81 +6146,81 @@
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="37" t="str">
-        <x:v>9.2</x:v>
+        <x:v>7.1</x:v>
       </x:c>
       <x:c r="B131" s="37" t="str">
-        <x:v>Study discontinuation at 24 months</x:v>
+        <x:v>NPI-Q score at 12 months</x:v>
       </x:c>
       <x:c r="C131" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D131" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="E131" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F131" s="43" t="n">
-        <x:v>1.008741777821183</x:v>
+        <x:v>0.08604846600191733</x:v>
       </x:c>
       <x:c r="G131" s="43" t="n">
-        <x:v>0.9411188324553125</x:v>
+        <x:v>-0.1834920094196857</x:v>
       </x:c>
       <x:c r="H131" s="43" t="n">
-        <x:v>1.081223687413734</x:v>
+        <x:v>0.3555889414235204</x:v>
       </x:c>
       <x:c r="I131" s="46" t="n">
-        <x:v>0.8058020547192906</x:v>
+        <x:v>0.5315107139042438</x:v>
       </x:c>
       <x:c r="J131" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K131" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="K131" s="49"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="37" t="str">
-        <x:v>9.2</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="B132" s="37" t="str">
-        <x:v>Study discontinuation at 24 months</x:v>
+        <x:v>NPI-Q score at 18 months</x:v>
       </x:c>
       <x:c r="C132" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D132" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="E132" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F132" s="43" t="n">
-        <x:v>1.05361653272101</x:v>
+        <x:v>0.1191993997701558</x:v>
       </x:c>
       <x:c r="G132" s="43" t="n">
-        <x:v>0.7888018745680653</x:v>
+        <x:v>-0.1747924558477071</x:v>
       </x:c>
       <x:c r="H132" s="43" t="n">
-        <x:v>1.407334127636195</x:v>
+        <x:v>0.4131912553880188</x:v>
       </x:c>
       <x:c r="I132" s="46" t="n">
-        <x:v>0.7236128240599273</x:v>
+        <x:v>0.4268054428964087</x:v>
       </x:c>
       <x:c r="J132" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K132" s="49"/>
+      <x:c r="K132" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="37" t="str">
-        <x:v>9.3</x:v>
+        <x:v>7.2</x:v>
       </x:c>
       <x:c r="B133" s="37" t="str">
-        <x:v>Study discontinuation above 24 months</x:v>
+        <x:v>NPI-Q score at 18 months</x:v>
       </x:c>
       <x:c r="C133" s="37" t="str">
-        <x:v>RR</x:v>
+        <x:v>SMD</x:v>
       </x:c>
       <x:c r="D133" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
@@ -6221,56 +6229,645 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F133" s="43" t="n">
+        <x:v>0.1191993997701558</x:v>
+      </x:c>
+      <x:c r="G133" s="43" t="n">
+        <x:v>-0.1747924558477071</x:v>
+      </x:c>
+      <x:c r="H133" s="43" t="n">
+        <x:v>0.4131912553880188</x:v>
+      </x:c>
+      <x:c r="I133" s="46" t="n">
+        <x:v>0.4268054428964087</x:v>
+      </x:c>
+      <x:c r="J133" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K133" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="37" t="str">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="B134" s="37" t="str">
+        <x:v>Infusion reaction at 18 months</x:v>
+      </x:c>
+      <x:c r="C134" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D134" s="37" t="str">
+        <x:v>Biomarker-confirmed</x:v>
+      </x:c>
+      <x:c r="E134" s="40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F134" s="43" t="n">
+        <x:v>3.580414000675478</x:v>
+      </x:c>
+      <x:c r="G134" s="43" t="n">
+        <x:v>0.06906491805724489</x:v>
+      </x:c>
+      <x:c r="H134" s="43" t="n">
+        <x:v>185.6132574515989</x:v>
+      </x:c>
+      <x:c r="I134" s="46" t="n">
+        <x:v>0.2990275366168896</x:v>
+      </x:c>
+      <x:c r="J134" s="43" t="n">
+        <x:v>2.363272780349808</x:v>
+      </x:c>
+      <x:c r="K134" s="49" t="n">
+        <x:v>97.19728094012109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="37" t="str">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="B135" s="37" t="str">
+        <x:v>Infusion reaction at 18 months</x:v>
+      </x:c>
+      <x:c r="C135" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D135" s="37" t="str">
+        <x:v>Cochrane class pool</x:v>
+      </x:c>
+      <x:c r="E135" s="40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F135" s="43" t="n">
+        <x:v>3.580414000675478</x:v>
+      </x:c>
+      <x:c r="G135" s="43" t="n">
+        <x:v>0.06906491805724489</x:v>
+      </x:c>
+      <x:c r="H135" s="43" t="n">
+        <x:v>185.6132574515989</x:v>
+      </x:c>
+      <x:c r="I135" s="46" t="n">
+        <x:v>0.2990275366168896</x:v>
+      </x:c>
+      <x:c r="J135" s="43" t="n">
+        <x:v>2.363272780349808</x:v>
+      </x:c>
+      <x:c r="K135" s="49" t="n">
+        <x:v>97.19728094012109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="37" t="str">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="B136" s="37" t="str">
+        <x:v>Infusion reaction at 18 months</x:v>
+      </x:c>
+      <x:c r="C136" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D136" s="37" t="str">
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+      </x:c>
+      <x:c r="E136" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F136" s="43" t="n">
+        <x:v>7.662918735750604</x:v>
+      </x:c>
+      <x:c r="G136" s="43" t="n">
+        <x:v>1.508711673369352</x:v>
+      </x:c>
+      <x:c r="H136" s="43" t="n">
+        <x:v>38.920838611647795</x:v>
+      </x:c>
+      <x:c r="I136" s="46" t="n">
+        <x:v>0.0140512231959229</x:v>
+      </x:c>
+      <x:c r="J136" s="43" t="n">
+        <x:v>1.246610367970227</x:v>
+      </x:c>
+      <x:c r="K136" s="49" t="n">
+        <x:v>89.95729838569783</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="37" t="str">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="B137" s="37" t="str">
+        <x:v>Infusion reaction at 18 months</x:v>
+      </x:c>
+      <x:c r="C137" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D137" s="37" t="str">
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+      </x:c>
+      <x:c r="E137" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F137" s="43" t="n">
+        <x:v>7.662918735750604</x:v>
+      </x:c>
+      <x:c r="G137" s="43" t="n">
+        <x:v>1.508711673369352</x:v>
+      </x:c>
+      <x:c r="H137" s="43" t="n">
+        <x:v>38.920838611647795</x:v>
+      </x:c>
+      <x:c r="I137" s="46" t="n">
+        <x:v>0.0140512231959229</x:v>
+      </x:c>
+      <x:c r="J137" s="43" t="n">
+        <x:v>1.246610367970227</x:v>
+      </x:c>
+      <x:c r="K137" s="49" t="n">
+        <x:v>89.95729838569783</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="37" t="str">
+        <x:v>8.1</x:v>
+      </x:c>
+      <x:c r="B138" s="37" t="str">
+        <x:v>Infusion reaction at 18 months</x:v>
+      </x:c>
+      <x:c r="C138" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D138" s="37" t="str">
+        <x:v>Response primary: clearing approved-generation trials</x:v>
+      </x:c>
+      <x:c r="E138" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F138" s="43" t="n">
+        <x:v>7.662918735750604</x:v>
+      </x:c>
+      <x:c r="G138" s="43" t="n">
+        <x:v>1.508711673369352</x:v>
+      </x:c>
+      <x:c r="H138" s="43" t="n">
+        <x:v>38.920838611647795</x:v>
+      </x:c>
+      <x:c r="I138" s="46" t="n">
+        <x:v>0.0140512231959229</x:v>
+      </x:c>
+      <x:c r="J138" s="43" t="n">
+        <x:v>1.246610367970227</x:v>
+      </x:c>
+      <x:c r="K138" s="49" t="n">
+        <x:v>89.95729838569783</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="37" t="str">
+        <x:v>8.2</x:v>
+      </x:c>
+      <x:c r="B139" s="37" t="str">
+        <x:v>Infusion reaction at 24 months</x:v>
+      </x:c>
+      <x:c r="C139" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D139" s="37" t="str">
+        <x:v>Biomarker-confirmed</x:v>
+      </x:c>
+      <x:c r="E139" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F139" s="43" t="n">
+        <x:v>1.149178942284472</x:v>
+      </x:c>
+      <x:c r="G139" s="43" t="n">
+        <x:v>0.7737788248778547</x:v>
+      </x:c>
+      <x:c r="H139" s="43" t="n">
+        <x:v>1.706705067302049</x:v>
+      </x:c>
+      <x:c r="I139" s="46" t="n">
+        <x:v>0.4907956322652618</x:v>
+      </x:c>
+      <x:c r="J139" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K139" s="49"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="37" t="str">
+        <x:v>8.2</x:v>
+      </x:c>
+      <x:c r="B140" s="37" t="str">
+        <x:v>Infusion reaction at 24 months</x:v>
+      </x:c>
+      <x:c r="C140" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D140" s="37" t="str">
+        <x:v>Cochrane class pool</x:v>
+      </x:c>
+      <x:c r="E140" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F140" s="43" t="n">
+        <x:v>1.149178942284472</x:v>
+      </x:c>
+      <x:c r="G140" s="43" t="n">
+        <x:v>0.7737788248778547</x:v>
+      </x:c>
+      <x:c r="H140" s="43" t="n">
+        <x:v>1.706705067302049</x:v>
+      </x:c>
+      <x:c r="I140" s="46" t="n">
+        <x:v>0.4907956322652618</x:v>
+      </x:c>
+      <x:c r="J140" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K140" s="49"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="37" t="str">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="B141" s="37" t="str">
+        <x:v>Study discontinuation at 18 months</x:v>
+      </x:c>
+      <x:c r="C141" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D141" s="37" t="str">
+        <x:v>Biomarker-confirmed</x:v>
+      </x:c>
+      <x:c r="E141" s="40" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F141" s="43" t="n">
+        <x:v>1.190649296916</x:v>
+      </x:c>
+      <x:c r="G141" s="43" t="n">
+        <x:v>0.9960323788259222</x:v>
+      </x:c>
+      <x:c r="H141" s="43" t="n">
+        <x:v>1.423292835035767</x:v>
+      </x:c>
+      <x:c r="I141" s="46" t="n">
+        <x:v>0.05360998308781049</x:v>
+      </x:c>
+      <x:c r="J141" s="43" t="n">
+        <x:v>0.01748992482403718</x:v>
+      </x:c>
+      <x:c r="K141" s="49" t="n">
+        <x:v>53.97889282539534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="37" t="str">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="B142" s="37" t="str">
+        <x:v>Study discontinuation at 18 months</x:v>
+      </x:c>
+      <x:c r="C142" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D142" s="37" t="str">
+        <x:v>Cochrane class pool</x:v>
+      </x:c>
+      <x:c r="E142" s="40" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F142" s="43" t="n">
+        <x:v>1.12069436507818</x:v>
+      </x:c>
+      <x:c r="G142" s="43" t="n">
+        <x:v>1.020569085776655</x:v>
+      </x:c>
+      <x:c r="H142" s="43" t="n">
+        <x:v>1.230642665373507</x:v>
+      </x:c>
+      <x:c r="I142" s="46" t="n">
+        <x:v>0.02182552233863456</x:v>
+      </x:c>
+      <x:c r="J142" s="43" t="n">
+        <x:v>0.009762441228302521</x:v>
+      </x:c>
+      <x:c r="K142" s="49" t="n">
+        <x:v>49.554731620791856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="37" t="str">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="B143" s="37" t="str">
+        <x:v>Study discontinuation at 18 months</x:v>
+      </x:c>
+      <x:c r="C143" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D143" s="37" t="str">
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+      </x:c>
+      <x:c r="E143" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F143" s="43" t="n">
+        <x:v>1.2932118172259</x:v>
+      </x:c>
+      <x:c r="G143" s="43" t="n">
+        <x:v>1.133286353220927</x:v>
+      </x:c>
+      <x:c r="H143" s="43" t="n">
+        <x:v>1.475705411487199</x:v>
+      </x:c>
+      <x:c r="I143" s="46" t="n">
+        <x:v>0.0001347038739540604</x:v>
+      </x:c>
+      <x:c r="J143" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K143" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="37" t="str">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="B144" s="37" t="str">
+        <x:v>Study discontinuation at 18 months</x:v>
+      </x:c>
+      <x:c r="C144" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D144" s="37" t="str">
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+      </x:c>
+      <x:c r="E144" s="40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F144" s="43" t="n">
+        <x:v>1.283807373552714</x:v>
+      </x:c>
+      <x:c r="G144" s="43" t="n">
+        <x:v>1.147356704309586</x:v>
+      </x:c>
+      <x:c r="H144" s="43" t="n">
+        <x:v>1.436485590050296</x:v>
+      </x:c>
+      <x:c r="I144" s="46" t="n">
+        <x:v>0.005805190402274013</x:v>
+      </x:c>
+      <x:c r="J144" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K144" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="37" t="str">
+        <x:v>9.1</x:v>
+      </x:c>
+      <x:c r="B145" s="37" t="str">
+        <x:v>Study discontinuation at 18 months</x:v>
+      </x:c>
+      <x:c r="C145" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D145" s="37" t="str">
+        <x:v>Response primary: clearing approved-generation trials</x:v>
+      </x:c>
+      <x:c r="E145" s="40" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F145" s="43" t="n">
+        <x:v>1.283807373552714</x:v>
+      </x:c>
+      <x:c r="G145" s="43" t="n">
+        <x:v>1.147356704309586</x:v>
+      </x:c>
+      <x:c r="H145" s="43" t="n">
+        <x:v>1.436485590050296</x:v>
+      </x:c>
+      <x:c r="I145" s="46" t="n">
+        <x:v>0.005805190402274013</x:v>
+      </x:c>
+      <x:c r="J145" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K145" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="37" t="str">
+        <x:v>9.2</x:v>
+      </x:c>
+      <x:c r="B146" s="37" t="str">
+        <x:v>Study discontinuation at 24 months</x:v>
+      </x:c>
+      <x:c r="C146" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D146" s="37" t="str">
+        <x:v>Biomarker-confirmed</x:v>
+      </x:c>
+      <x:c r="E146" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F146" s="43" t="n">
+        <x:v>1.008741777821183</x:v>
+      </x:c>
+      <x:c r="G146" s="43" t="n">
+        <x:v>0.9411188324553125</x:v>
+      </x:c>
+      <x:c r="H146" s="43" t="n">
+        <x:v>1.081223687413734</x:v>
+      </x:c>
+      <x:c r="I146" s="46" t="n">
+        <x:v>0.8058020547192906</x:v>
+      </x:c>
+      <x:c r="J146" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K146" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="37" t="str">
+        <x:v>9.2</x:v>
+      </x:c>
+      <x:c r="B147" s="37" t="str">
+        <x:v>Study discontinuation at 24 months</x:v>
+      </x:c>
+      <x:c r="C147" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D147" s="37" t="str">
+        <x:v>Cochrane class pool</x:v>
+      </x:c>
+      <x:c r="E147" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F147" s="43" t="n">
+        <x:v>1.008741777821183</x:v>
+      </x:c>
+      <x:c r="G147" s="43" t="n">
+        <x:v>0.9411188324553125</x:v>
+      </x:c>
+      <x:c r="H147" s="43" t="n">
+        <x:v>1.081223687413734</x:v>
+      </x:c>
+      <x:c r="I147" s="46" t="n">
+        <x:v>0.8058020547192906</x:v>
+      </x:c>
+      <x:c r="J147" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K147" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="37" t="str">
+        <x:v>9.2</x:v>
+      </x:c>
+      <x:c r="B148" s="37" t="str">
+        <x:v>Study discontinuation at 24 months</x:v>
+      </x:c>
+      <x:c r="C148" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D148" s="37" t="str">
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+      </x:c>
+      <x:c r="E148" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F148" s="43" t="n">
+        <x:v>1.05361653272101</x:v>
+      </x:c>
+      <x:c r="G148" s="43" t="n">
+        <x:v>0.7888018745680653</x:v>
+      </x:c>
+      <x:c r="H148" s="43" t="n">
+        <x:v>1.407334127636195</x:v>
+      </x:c>
+      <x:c r="I148" s="46" t="n">
+        <x:v>0.7236128240599273</x:v>
+      </x:c>
+      <x:c r="J148" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K148" s="49"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="37" t="str">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="B149" s="37" t="str">
+        <x:v>Study discontinuation above 24 months</x:v>
+      </x:c>
+      <x:c r="C149" s="37" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D149" s="37" t="str">
+        <x:v>Biomarker-confirmed</x:v>
+      </x:c>
+      <x:c r="E149" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F149" s="43" t="n">
         <x:v>1.355002688994968</x:v>
       </x:c>
-      <x:c r="G133" s="43" t="n">
+      <x:c r="G149" s="43" t="n">
         <x:v>1.109422105329669</x:v>
       </x:c>
-      <x:c r="H133" s="43" t="n">
+      <x:c r="H149" s="43" t="n">
         <x:v>1.654944748588734</x:v>
       </x:c>
-      <x:c r="I133" s="46" t="n">
+      <x:c r="I149" s="46" t="n">
         <x:v>0.002903706094042277</x:v>
       </x:c>
-      <x:c r="J133" s="43" t="n">
+      <x:c r="J149" s="43" t="n">
         <x:v>0.005604882658618307</x:v>
       </x:c>
-      <x:c r="K133" s="49" t="n">
+      <x:c r="K149" s="49" t="n">
         <x:v>26.85324966478464</x:v>
       </x:c>
     </x:row>
-    <x:row r="134">
-      <x:c r="A134" s="38" t="str">
+    <x:row r="150">
+      <x:c r="A150" s="37" t="str">
         <x:v>9.3</x:v>
       </x:c>
-      <x:c r="B134" s="38" t="str">
+      <x:c r="B150" s="37" t="str">
         <x:v>Study discontinuation above 24 months</x:v>
       </x:c>
-      <x:c r="C134" s="38" t="str">
+      <x:c r="C150" s="37" t="str">
         <x:v>RR</x:v>
       </x:c>
-      <x:c r="D134" s="38" t="str">
+      <x:c r="D150" s="37" t="str">
+        <x:v>Cochrane class pool</x:v>
+      </x:c>
+      <x:c r="E150" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F150" s="43" t="n">
+        <x:v>1.355002688994968</x:v>
+      </x:c>
+      <x:c r="G150" s="43" t="n">
+        <x:v>1.109422105329669</x:v>
+      </x:c>
+      <x:c r="H150" s="43" t="n">
+        <x:v>1.654944748588734</x:v>
+      </x:c>
+      <x:c r="I150" s="46" t="n">
+        <x:v>0.002903706094042277</x:v>
+      </x:c>
+      <x:c r="J150" s="43" t="n">
+        <x:v>0.005604882658618307</x:v>
+      </x:c>
+      <x:c r="K150" s="49" t="n">
+        <x:v>26.85324966478464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="38" t="str">
+        <x:v>9.3</x:v>
+      </x:c>
+      <x:c r="B151" s="38" t="str">
+        <x:v>Study discontinuation above 24 months</x:v>
+      </x:c>
+      <x:c r="C151" s="38" t="str">
+        <x:v>RR</x:v>
+      </x:c>
+      <x:c r="D151" s="38" t="str">
         <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
-      <x:c r="E134" s="41" t="n">
+      <x:c r="E151" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F134" s="44" t="n">
+      <x:c r="F151" s="44" t="n">
         <x:v>1.355002688994968</x:v>
       </x:c>
-      <x:c r="G134" s="44" t="n">
+      <x:c r="G151" s="44" t="n">
         <x:v>1.109422105329669</x:v>
       </x:c>
-      <x:c r="H134" s="44" t="n">
+      <x:c r="H151" s="44" t="n">
         <x:v>1.654944748588734</x:v>
       </x:c>
-      <x:c r="I134" s="47" t="n">
+      <x:c r="I151" s="47" t="n">
         <x:v>0.002903706094042277</x:v>
       </x:c>
-      <x:c r="J134" s="44" t="n">
+      <x:c r="J151" s="44" t="n">
         <x:v>0.005604882658618307</x:v>
       </x:c>
-      <x:c r="K134" s="50" t="n">
+      <x:c r="K151" s="50" t="n">
         <x:v>26.85324966478464</x:v>
       </x:c>
     </x:row>
@@ -6281,7 +6878,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91ffdb51fa96402b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc5d378884894e1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6512,7 +7109,7 @@
         <x:v>ADAS-Cog scale above 24 months</x:v>
       </x:c>
       <x:c r="C10" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D10" s="40" t="n">
         <x:v>2</x:v>
@@ -6544,7 +7141,7 @@
         <x:v>ADAS-Cog scale above 24 months</x:v>
       </x:c>
       <x:c r="C11" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D11" s="40" t="n">
         <x:v>2</x:v>
@@ -6570,34 +7167,34 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="37" t="str">
-        <x:v>1.4</x:v>
+        <x:v>1.3</x:v>
       </x:c>
       <x:c r="B12" s="37" t="str">
-        <x:v>MMSE scale at 18 months</x:v>
+        <x:v>ADAS-Cog scale above 24 months</x:v>
       </x:c>
       <x:c r="C12" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="D12" s="40" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E12" s="43" t="n">
-        <x:v>0.8709530268258416</x:v>
+        <x:v>-1.267015483438359</x:v>
       </x:c>
       <x:c r="F12" s="43" t="n">
-        <x:v>-0.5504904424339689</x:v>
+        <x:v>-2.219629855240101</x:v>
       </x:c>
       <x:c r="G12" s="43" t="n">
-        <x:v>2.292396496085652</x:v>
+        <x:v>-0.3144011116366178</x:v>
       </x:c>
       <x:c r="H12" s="46" t="n">
-        <x:v>0.1844609969623976</x:v>
+        <x:v>0.009138444036168814</x:v>
       </x:c>
       <x:c r="I12" s="43" t="n">
-        <x:v>1.708676470674428</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J12" s="49" t="n">
-        <x:v>94.07806866531021</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6608,28 +7205,28 @@
         <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C13" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D13" s="40" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E13" s="43" t="n">
-        <x:v>0.8491660202540409</x:v>
+        <x:v>0.8709530268258416</x:v>
       </x:c>
       <x:c r="F13" s="43" t="n">
-        <x:v>-0.2972188485605277</x:v>
+        <x:v>-0.5504904424339689</x:v>
       </x:c>
       <x:c r="G13" s="43" t="n">
-        <x:v>1.99555088906861</x:v>
+        <x:v>2.292396496085652</x:v>
       </x:c>
       <x:c r="H13" s="46" t="n">
-        <x:v>0.1233125510932536</x:v>
+        <x:v>0.1844609969623976</x:v>
       </x:c>
       <x:c r="I13" s="43" t="n">
-        <x:v>1.236997235003846</x:v>
+        <x:v>1.708676470674428</x:v>
       </x:c>
       <x:c r="J13" s="49" t="n">
-        <x:v>92.185820280217</x:v>
+        <x:v>94.07806866531021</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6640,27 +7237,29 @@
         <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C14" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D14" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E14" s="43" t="n">
-        <x:v>0.5700000000000003</x:v>
+        <x:v>0.8491660202540409</x:v>
       </x:c>
       <x:c r="F14" s="43" t="n">
-        <x:v>0.1401463293702058</x:v>
+        <x:v>-0.2972188485605277</x:v>
       </x:c>
       <x:c r="G14" s="43" t="n">
-        <x:v>0.9998536706297948</x:v>
+        <x:v>1.99555088906861</x:v>
       </x:c>
       <x:c r="H14" s="46" t="n">
-        <x:v>0.009350224836172299</x:v>
+        <x:v>0.1233125510932536</x:v>
       </x:c>
       <x:c r="I14" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="49"/>
+        <x:v>1.236997235003846</x:v>
+      </x:c>
+      <x:c r="J14" s="49" t="n">
+        <x:v>92.185820280217</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="37" t="str">
@@ -6670,29 +7269,27 @@
         <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C15" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="D15" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="43" t="n">
-        <x:v>0.3571813275838583</x:v>
+        <x:v>0.5700000000000003</x:v>
       </x:c>
       <x:c r="F15" s="43" t="n">
-        <x:v>-0.1883187214340558</x:v>
+        <x:v>0.1401463293702058</x:v>
       </x:c>
       <x:c r="G15" s="43" t="n">
-        <x:v>0.9026813766017723</x:v>
+        <x:v>0.9998536706297948</x:v>
       </x:c>
       <x:c r="H15" s="46" t="n">
-        <x:v>0.1285357896952432</x:v>
+        <x:v>0.009350224836172299</x:v>
       </x:c>
       <x:c r="I15" s="43" t="n">
-        <x:v>0.04576409731591151</x:v>
-      </x:c>
-      <x:c r="J15" s="49" t="n">
-        <x:v>35.16589789141264</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J15" s="49"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="37" t="str">
@@ -6702,60 +7299,60 @@
         <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C16" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="D16" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E16" s="43" t="n">
-        <x:v>0.3760620115530059</x:v>
+        <x:v>0.3571813275838583</x:v>
       </x:c>
       <x:c r="F16" s="43" t="n">
-        <x:v>-0.5803964814162018</x:v>
+        <x:v>-0.1883187214340558</x:v>
       </x:c>
       <x:c r="G16" s="43" t="n">
-        <x:v>1.332520504522213</x:v>
+        <x:v>0.9026813766017723</x:v>
       </x:c>
       <x:c r="H16" s="46" t="n">
-        <x:v>0.2327706546525998</x:v>
+        <x:v>0.1285357896952432</x:v>
       </x:c>
       <x:c r="I16" s="43" t="n">
-        <x:v>0.07399872511758346</x:v>
+        <x:v>0.04576409731591151</x:v>
       </x:c>
       <x:c r="J16" s="49" t="n">
-        <x:v>52.17774309573512</x:v>
+        <x:v>35.16589789141264</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="37" t="str">
-        <x:v>2.1</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="B17" s="37" t="str">
-        <x:v>CDR-SB scale at 18 months</x:v>
+        <x:v>MMSE scale at 18 months</x:v>
       </x:c>
       <x:c r="C17" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="D17" s="40" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E17" s="43" t="n">
-        <x:v>-0.3053058344254157</x:v>
+        <x:v>0.3760620115530059</x:v>
       </x:c>
       <x:c r="F17" s="43" t="n">
-        <x:v>-0.6549196733530472</x:v>
+        <x:v>-0.5803964814162018</x:v>
       </x:c>
       <x:c r="G17" s="43" t="n">
-        <x:v>0.04430800450221584</x:v>
+        <x:v>1.332520504522213</x:v>
       </x:c>
       <x:c r="H17" s="46" t="n">
-        <x:v>0.07779505869558745</x:v>
+        <x:v>0.2327706546525998</x:v>
       </x:c>
       <x:c r="I17" s="43" t="n">
-        <x:v>0.07296776781612903</x:v>
+        <x:v>0.07399872511758346</x:v>
       </x:c>
       <x:c r="J17" s="49" t="n">
-        <x:v>70.77709381997417</x:v>
+        <x:v>52.17774309573512</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6766,28 +7363,28 @@
         <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C18" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D18" s="40" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="43" t="n">
-        <x:v>-0.2916091699352105</x:v>
+        <x:v>-0.3053058344254157</x:v>
       </x:c>
       <x:c r="F18" s="43" t="n">
-        <x:v>-0.5827770296388439</x:v>
+        <x:v>-0.6549196733530472</x:v>
       </x:c>
       <x:c r="G18" s="43" t="n">
-        <x:v>-0.0004413102315771744</x:v>
+        <x:v>0.04430800450221584</x:v>
       </x:c>
       <x:c r="H18" s="46" t="n">
-        <x:v>0.04972794206433728</x:v>
+        <x:v>0.07779505869558745</x:v>
       </x:c>
       <x:c r="I18" s="43" t="n">
-        <x:v>0.05821159810982466</x:v>
+        <x:v>0.07296776781612903</x:v>
       </x:c>
       <x:c r="J18" s="49" t="n">
-        <x:v>65.78390042307639</x:v>
+        <x:v>70.77709381997417</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6798,28 +7395,28 @@
         <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C19" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D19" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E19" s="43" t="n">
-        <x:v>-0.5640644275317617</x:v>
+        <x:v>-0.2916091699352105</x:v>
       </x:c>
       <x:c r="F19" s="43" t="n">
-        <x:v>-0.8081205819637447</x:v>
+        <x:v>-0.5827770296388439</x:v>
       </x:c>
       <x:c r="G19" s="43" t="n">
-        <x:v>-0.3200082730997786</x:v>
+        <x:v>-0.0004413102315771744</x:v>
       </x:c>
       <x:c r="H19" s="46" t="n">
-        <x:v>0.000005901620124870172</x:v>
+        <x:v>0.04972794206433728</x:v>
       </x:c>
       <x:c r="I19" s="43" t="n">
-        <x:v>0.01588388948729768</x:v>
+        <x:v>0.05821159810982466</x:v>
       </x:c>
       <x:c r="J19" s="49" t="n">
-        <x:v>50.8284463593526</x:v>
+        <x:v>65.78390042307639</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6830,28 +7427,28 @@
         <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C20" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="D20" s="40" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E20" s="43" t="n">
-        <x:v>-0.3138970943515159</x:v>
+        <x:v>-0.5640644275317617</x:v>
       </x:c>
       <x:c r="F20" s="43" t="n">
-        <x:v>-0.7290074017606135</x:v>
+        <x:v>-0.8081205819637447</x:v>
       </x:c>
       <x:c r="G20" s="43" t="n">
-        <x:v>0.1012132130575818</x:v>
+        <x:v>-0.3200082730997786</x:v>
       </x:c>
       <x:c r="H20" s="46" t="n">
-        <x:v>0.103713512748568</x:v>
+        <x:v>0.000005901620124870172</x:v>
       </x:c>
       <x:c r="I20" s="43" t="n">
-        <x:v>0.08022751588226375</x:v>
+        <x:v>0.01588388948729768</x:v>
       </x:c>
       <x:c r="J20" s="49" t="n">
-        <x:v>77.84682289380306</x:v>
+        <x:v>50.8284463593526</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -6862,60 +7459,60 @@
         <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C21" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="D21" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E21" s="43" t="n">
-        <x:v>-0.3852628775661823</x:v>
+        <x:v>-0.3138970943515159</x:v>
       </x:c>
       <x:c r="F21" s="43" t="n">
-        <x:v>-0.8613981149280898</x:v>
+        <x:v>-0.7290074017606135</x:v>
       </x:c>
       <x:c r="G21" s="43" t="n">
-        <x:v>0.09087235979572533</x:v>
+        <x:v>0.1012132130575818</x:v>
       </x:c>
       <x:c r="H21" s="46" t="n">
-        <x:v>0.0821309945244652</x:v>
+        <x:v>0.103713512748568</x:v>
       </x:c>
       <x:c r="I21" s="43" t="n">
-        <x:v>0.06808577081146662</x:v>
+        <x:v>0.08022751588226375</x:v>
       </x:c>
       <x:c r="J21" s="49" t="n">
-        <x:v>78.36346559911865</x:v>
+        <x:v>77.84682289380306</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="37" t="str">
-        <x:v>2.3</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="B22" s="37" t="str">
-        <x:v>CDR-SB scale above 24 months</x:v>
+        <x:v>CDR-SB scale at 18 months</x:v>
       </x:c>
       <x:c r="C22" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Response primary: clearing approved-generation trials</x:v>
       </x:c>
       <x:c r="D22" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E22" s="43" t="n">
-        <x:v>-0.227514320809825</x:v>
+        <x:v>-0.3852628775661823</x:v>
       </x:c>
       <x:c r="F22" s="43" t="n">
-        <x:v>-0.5168827865852184</x:v>
+        <x:v>-0.8613981149280898</x:v>
       </x:c>
       <x:c r="G22" s="43" t="n">
-        <x:v>0.06185414496556835</x:v>
+        <x:v>0.09087235979572533</x:v>
       </x:c>
       <x:c r="H22" s="46" t="n">
-        <x:v>0.1233142047594829</x:v>
+        <x:v>0.0821309945244652</x:v>
       </x:c>
       <x:c r="I22" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>0.06808577081146662</x:v>
       </x:c>
       <x:c r="J22" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>78.36346559911865</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -6926,7 +7523,7 @@
         <x:v>CDR-SB scale above 24 months</x:v>
       </x:c>
       <x:c r="C23" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D23" s="40" t="n">
         <x:v>2</x:v>
@@ -6952,60 +7549,60 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="37" t="str">
-        <x:v>3.1</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="B24" s="37" t="str">
-        <x:v>DAD total score at 18 months</x:v>
+        <x:v>CDR-SB scale above 24 months</x:v>
       </x:c>
       <x:c r="C24" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D24" s="40" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E24" s="43" t="n">
-        <x:v>0.7424137711537498</x:v>
+        <x:v>-0.227514320809825</x:v>
       </x:c>
       <x:c r="F24" s="43" t="n">
-        <x:v>-3.01091018604994</x:v>
+        <x:v>-0.5168827865852184</x:v>
       </x:c>
       <x:c r="G24" s="43" t="n">
-        <x:v>4.495737728357439</x:v>
+        <x:v>0.06185414496556835</x:v>
       </x:c>
       <x:c r="H24" s="46" t="n">
-        <x:v>0.5737006232602254</x:v>
+        <x:v>0.1233142047594829</x:v>
       </x:c>
       <x:c r="I24" s="43" t="n">
-        <x:v>2.690330122910305</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J24" s="49" t="n">
-        <x:v>47.77267168178479</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="37" t="str">
-        <x:v>3.2</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="B25" s="37" t="str">
-        <x:v>ADCS-ADL score at 18 months</x:v>
+        <x:v>CDR-SB scale above 24 months</x:v>
       </x:c>
       <x:c r="C25" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="D25" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E25" s="43" t="n">
-        <x:v>1.256965753220758</x:v>
+        <x:v>-0.227514320809825</x:v>
       </x:c>
       <x:c r="F25" s="43" t="n">
-        <x:v>0.08755052982404199</x:v>
+        <x:v>-0.5168827865852184</x:v>
       </x:c>
       <x:c r="G25" s="43" t="n">
-        <x:v>2.426380976617475</x:v>
+        <x:v>0.06185414496556835</x:v>
       </x:c>
       <x:c r="H25" s="46" t="n">
-        <x:v>0.03514355105106162</x:v>
+        <x:v>0.1233142047594829</x:v>
       </x:c>
       <x:c r="I25" s="43" t="n">
         <x:v>0</x:v>
@@ -7016,60 +7613,60 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="37" t="str">
-        <x:v>3.2</x:v>
+        <x:v>3.1</x:v>
       </x:c>
       <x:c r="B26" s="37" t="str">
-        <x:v>ADCS-ADL score at 18 months</x:v>
+        <x:v>DAD total score at 18 months</x:v>
       </x:c>
       <x:c r="C26" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D26" s="40" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E26" s="43" t="n">
-        <x:v>1.315326183286629</x:v>
+        <x:v>0.7424137711537498</x:v>
       </x:c>
       <x:c r="F26" s="43" t="n">
-        <x:v>0.6195253236913434</x:v>
+        <x:v>-3.01091018604994</x:v>
       </x:c>
       <x:c r="G26" s="43" t="n">
-        <x:v>2.011127042881915</x:v>
+        <x:v>4.495737728357439</x:v>
       </x:c>
       <x:c r="H26" s="46" t="n">
-        <x:v>0.01478145643952042</x:v>
+        <x:v>0.5737006232602254</x:v>
       </x:c>
       <x:c r="I26" s="43" t="n">
-        <x:v>0</x:v>
+        <x:v>2.690330122910305</x:v>
       </x:c>
       <x:c r="J26" s="49" t="n">
-        <x:v>0</x:v>
+        <x:v>47.77267168178479</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="37" t="str">
-        <x:v>3.4</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="B27" s="37" t="str">
-        <x:v>ADCS-ADL score above 24 months</x:v>
+        <x:v>ADCS-ADL score at 18 months</x:v>
       </x:c>
       <x:c r="C27" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D27" s="40" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E27" s="43" t="n">
-        <x:v>0.9542616730399138</x:v>
+        <x:v>1.256965753220758</x:v>
       </x:c>
       <x:c r="F27" s="43" t="n">
-        <x:v>-0.2651608954893963</x:v>
+        <x:v>0.08755052982404199</x:v>
       </x:c>
       <x:c r="G27" s="43" t="n">
-        <x:v>2.173684241569224</x:v>
+        <x:v>2.426380976617475</x:v>
       </x:c>
       <x:c r="H27" s="46" t="n">
-        <x:v>0.1250852855890333</x:v>
+        <x:v>0.03514355105106162</x:v>
       </x:c>
       <x:c r="I27" s="43" t="n">
         <x:v>0</x:v>
@@ -7080,28 +7677,28 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="37" t="str">
-        <x:v>3.4</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="B28" s="37" t="str">
-        <x:v>ADCS-ADL score above 24 months</x:v>
+        <x:v>ADCS-ADL score at 18 months</x:v>
       </x:c>
       <x:c r="C28" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D28" s="40" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E28" s="43" t="n">
-        <x:v>0.9542616730399138</x:v>
+        <x:v>1.315326183286629</x:v>
       </x:c>
       <x:c r="F28" s="43" t="n">
-        <x:v>-0.2651608954893963</x:v>
+        <x:v>0.6195253236913434</x:v>
       </x:c>
       <x:c r="G28" s="43" t="n">
-        <x:v>2.173684241569224</x:v>
+        <x:v>2.011127042881915</x:v>
       </x:c>
       <x:c r="H28" s="46" t="n">
-        <x:v>0.1250852855890333</x:v>
+        <x:v>0.01478145643952042</x:v>
       </x:c>
       <x:c r="I28" s="43" t="n">
         <x:v>0</x:v>
@@ -7112,93 +7709,99 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="B29" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score above 24 months</x:v>
       </x:c>
       <x:c r="C29" s="37" t="str">
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D29" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E29" s="43" t="n">
-        <x:v>1.75</x:v>
+        <x:v>0.9542616730399138</x:v>
       </x:c>
       <x:c r="F29" s="43" t="n">
-        <x:v>0.8213410087695308</x:v>
+        <x:v>-0.2651608954893963</x:v>
       </x:c>
       <x:c r="G29" s="43" t="n">
-        <x:v>2.678658991230469</x:v>
+        <x:v>2.173684241569224</x:v>
       </x:c>
       <x:c r="H29" s="46" t="n">
-        <x:v>0.0002212494383262123</x:v>
+        <x:v>0.1250852855890333</x:v>
       </x:c>
       <x:c r="I29" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J29" s="49"/>
+      <x:c r="J29" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="B30" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score above 24 months</x:v>
       </x:c>
       <x:c r="C30" s="37" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D30" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E30" s="43" t="n">
-        <x:v>1.75</x:v>
+        <x:v>0.9542616730399138</x:v>
       </x:c>
       <x:c r="F30" s="43" t="n">
-        <x:v>0.8213410087695308</x:v>
+        <x:v>-0.2651608954893963</x:v>
       </x:c>
       <x:c r="G30" s="43" t="n">
-        <x:v>2.678658991230469</x:v>
+        <x:v>2.173684241569224</x:v>
       </x:c>
       <x:c r="H30" s="46" t="n">
-        <x:v>0.0002212494383262123</x:v>
+        <x:v>0.1250852855890333</x:v>
       </x:c>
       <x:c r="I30" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J30" s="49"/>
+      <x:c r="J30" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="37" t="str">
-        <x:v>3.6</x:v>
+        <x:v>3.4</x:v>
       </x:c>
       <x:c r="B31" s="37" t="str">
-        <x:v>ADCS-iADL score at 18 months</x:v>
+        <x:v>ADCS-ADL score above 24 months</x:v>
       </x:c>
       <x:c r="C31" s="37" t="str">
-        <x:v>Currently active agents: lecanemab + donanemab</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="D31" s="40" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E31" s="43" t="n">
-        <x:v>1.75</x:v>
+        <x:v>0.9542616730399138</x:v>
       </x:c>
       <x:c r="F31" s="43" t="n">
-        <x:v>0.8213410087695308</x:v>
+        <x:v>-0.2651608954893963</x:v>
       </x:c>
       <x:c r="G31" s="43" t="n">
-        <x:v>2.678658991230469</x:v>
+        <x:v>2.173684241569224</x:v>
       </x:c>
       <x:c r="H31" s="46" t="n">
-        <x:v>0.0002212494383262123</x:v>
+        <x:v>0.1250852855890333</x:v>
       </x:c>
       <x:c r="I31" s="43" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J31" s="49"/>
+      <x:c r="J31" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="37" t="str">
@@ -7208,7 +7811,7 @@
         <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C32" s="37" t="str">
-        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
+        <x:v>Biomarker-confirmed</x:v>
       </x:c>
       <x:c r="D32" s="40" t="n">
         <x:v>1</x:v>
@@ -7238,7 +7841,7 @@
         <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C33" s="37" t="str">
-        <x:v>Response primary: clearing approved-generation trials</x:v>
+        <x:v>Cochrane class pool</x:v>
       </x:c>
       <x:c r="D33" s="40" t="n">
         <x:v>1</x:v>
@@ -7262,28 +7865,28 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="37" t="str">
-        <x:v>7.1</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B34" s="37" t="str">
-        <x:v>NPI-Q score at 12 months</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C34" s="37" t="str">
-        <x:v>Biomarker-confirmed</x:v>
+        <x:v>Currently active agents: lecanemab + donanemab</x:v>
       </x:c>
       <x:c r="D34" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E34" s="43" t="n">
-        <x:v>0.76</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="F34" s="43" t="n">
-        <x:v>-1.60030893359543</x:v>
+        <x:v>0.8213410087695308</x:v>
       </x:c>
       <x:c r="G34" s="43" t="n">
-        <x:v>3.12030893359543</x:v>
+        <x:v>2.678658991230469</x:v>
       </x:c>
       <x:c r="H34" s="46" t="n">
-        <x:v>0.5279802213160714</x:v>
+        <x:v>0.0002212494383262123</x:v>
       </x:c>
       <x:c r="I34" s="43" t="n">
         <x:v>0</x:v>
@@ -7292,28 +7895,28 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="37" t="str">
-        <x:v>7.1</x:v>
+        <x:v>3.6</x:v>
       </x:c>
       <x:c r="B35" s="37" t="str">
-        <x:v>NPI-Q score at 12 months</x:v>
+        <x:v>ADCS-iADL score at 18 months</x:v>
       </x:c>
       <x:c r="C35" s="37" t="str">
-        <x:v>Cochrane class pool</x:v>
+        <x:v>Demonstrated clearance: &gt;=10 CL</x:v>
       </x:c>
       <x:c r="D35" s="40" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E35" s="43" t="n">
-        <x:v>0.76</x:v>
+        <x:v>1.75</x:v>
       </x:c>
       <x:c r="F35" s="43" t="n">
-        <x:v>-1.60030893359543</x:v>
+        <x:v>0.8213410087695308</x:v>
       </x:c>
       <x:c r="G35" s="43" t="n">
-        <x:v>3.12030893359543</x:v>
+        <x:v>2.678658991230469</x:v>
       </x:c>
       <x:c r="H35" s="46" t="n">
-        <x:v>0.5279802213160714</x:v>
+        <x:v>0.0002212494383262123</x:v>
       </x:c>
       <x:c r="I35" s="43" t="n">
         <x:v>0</x:v>
@@ -7322,63 +7925,155 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="37" t="str">
+        <x:v>3.6</x:v>
+      </x:c>
+      <x:c r="B36" s="37" t="str">
+        <x:v>ADCS-iADL score at 18 months</x:v>
+      </x:c>
+      <x:c r="C36" s="37" t="str">
+        <x:v>Response primary: clearing approved-generation trials</x:v>
+      </x:c>
+      <x:c r="D36" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E36" s="43" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="F36" s="43" t="n">
+        <x:v>0.8213410087695308</x:v>
+      </x:c>
+      <x:c r="G36" s="43" t="n">
+        <x:v>2.678658991230469</x:v>
+      </x:c>
+      <x:c r="H36" s="46" t="n">
+        <x:v>0.0002212494383262123</x:v>
+      </x:c>
+      <x:c r="I36" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J36" s="49"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="37" t="str">
+        <x:v>7.1</x:v>
+      </x:c>
+      <x:c r="B37" s="37" t="str">
+        <x:v>NPI-Q score at 12 months</x:v>
+      </x:c>
+      <x:c r="C37" s="37" t="str">
+        <x:v>Biomarker-confirmed</x:v>
+      </x:c>
+      <x:c r="D37" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E37" s="43" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="F37" s="43" t="n">
+        <x:v>-1.60030893359543</x:v>
+      </x:c>
+      <x:c r="G37" s="43" t="n">
+        <x:v>3.12030893359543</x:v>
+      </x:c>
+      <x:c r="H37" s="46" t="n">
+        <x:v>0.5279802213160714</x:v>
+      </x:c>
+      <x:c r="I37" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J37" s="49"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="37" t="str">
+        <x:v>7.1</x:v>
+      </x:c>
+      <x:c r="B38" s="37" t="str">
+        <x:v>NPI-Q score at 12 months</x:v>
+      </x:c>
+      <x:c r="C38" s="37" t="str">
+        <x:v>Cochrane class pool</x:v>
+      </x:c>
+      <x:c r="D38" s="40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E38" s="43" t="n">
+        <x:v>0.76</x:v>
+      </x:c>
+      <x:c r="F38" s="43" t="n">
+        <x:v>-1.60030893359543</x:v>
+      </x:c>
+      <x:c r="G38" s="43" t="n">
+        <x:v>3.12030893359543</x:v>
+      </x:c>
+      <x:c r="H38" s="46" t="n">
+        <x:v>0.5279802213160714</x:v>
+      </x:c>
+      <x:c r="I38" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J38" s="49"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="37" t="str">
         <x:v>7.2</x:v>
       </x:c>
-      <x:c r="B36" s="37" t="str">
+      <x:c r="B39" s="37" t="str">
         <x:v>NPI-Q score at 18 months</x:v>
       </x:c>
-      <x:c r="C36" s="37" t="str">
+      <x:c r="C39" s="37" t="str">
         <x:v>Biomarker-confirmed</x:v>
       </x:c>
-      <x:c r="D36" s="40" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E36" s="43" t="n">
-        <x:v>6.500000000000001</x:v>
-      </x:c>
-      <x:c r="F36" s="43" t="n">
-        <x:v>-12.81461920011882</x:v>
-      </x:c>
-      <x:c r="G36" s="43" t="n">
-        <x:v>25.81461920011882</x:v>
-      </x:c>
-      <x:c r="H36" s="46" t="n">
-        <x:v>0.5095157694796356</x:v>
-      </x:c>
-      <x:c r="I36" s="43" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J36" s="49"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="38" t="str">
+      <x:c r="D39" s="40" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E39" s="43" t="n">
+        <x:v>0.5676844941718961</x:v>
+      </x:c>
+      <x:c r="F39" s="43" t="n">
+        <x:v>-0.9668629836069913</x:v>
+      </x:c>
+      <x:c r="G39" s="43" t="n">
+        <x:v>2.102231971950784</x:v>
+      </x:c>
+      <x:c r="H39" s="46" t="n">
+        <x:v>0.4684143552333707</x:v>
+      </x:c>
+      <x:c r="I39" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J39" s="49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="38" t="str">
         <x:v>7.2</x:v>
       </x:c>
-      <x:c r="B37" s="38" t="str">
+      <x:c r="B40" s="38" t="str">
         <x:v>NPI-Q score at 18 months</x:v>
       </x:c>
-      <x:c r="C37" s="38" t="str">
+      <x:c r="C40" s="38" t="str">
         <x:v>Cochrane class pool</x:v>
       </x:c>
-      <x:c r="D37" s="41" t="n">
+      <x:c r="D40" s="41" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E37" s="44" t="n">
+      <x:c r="E40" s="44" t="n">
         <x:v>0.5676844941718961</x:v>
       </x:c>
-      <x:c r="F37" s="44" t="n">
+      <x:c r="F40" s="44" t="n">
         <x:v>-0.9668629836069913</x:v>
       </x:c>
-      <x:c r="G37" s="44" t="n">
+      <x:c r="G40" s="44" t="n">
         <x:v>2.102231971950784</x:v>
       </x:c>
-      <x:c r="H37" s="47" t="n">
+      <x:c r="H40" s="47" t="n">
         <x:v>0.4684143552333707</x:v>
       </x:c>
-      <x:c r="I37" s="44" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J37" s="50" t="n">
+      <x:c r="I40" s="44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J40" s="50" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -7389,7 +8084,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R354aba9824f84dda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44074f9d04de47b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7657,7 +8352,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a950113859147cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe3c12a138924c2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7931,7 +8626,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fc1ac08074141c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4f29550f8f943b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9424,7 +10119,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcf6054c741f467a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0320e9414b1d4e66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10278,7 +10973,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N18" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O18" s="72" t="b">
         <x:v>0</x:v>
@@ -10334,7 +11029,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N19" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O19" s="72" t="b">
         <x:v>0</x:v>
@@ -10388,7 +11083,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N20" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O20" s="72" t="b">
         <x:v>0</x:v>
@@ -10442,7 +11137,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N21" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O21" s="72" t="b">
         <x:v>0</x:v>
@@ -10940,7 +11635,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N30" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O30" s="72" t="b">
         <x:v>0</x:v>
@@ -10996,7 +11691,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N31" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O31" s="72" t="b">
         <x:v>0</x:v>
@@ -11046,7 +11741,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N32" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O32" s="72" t="b">
         <x:v>0</x:v>
@@ -11096,7 +11791,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N33" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O33" s="72" t="b">
         <x:v>0</x:v>
@@ -11650,7 +12345,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N43" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O43" s="72" t="b">
         <x:v>0</x:v>
@@ -11706,7 +12401,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N44" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O44" s="72" t="b">
         <x:v>0</x:v>
@@ -11760,7 +12455,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N45" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O45" s="72" t="b">
         <x:v>0</x:v>
@@ -11814,7 +12509,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N46" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O46" s="72" t="b">
         <x:v>0</x:v>
@@ -11864,7 +12559,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N47" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O47" s="72" t="b">
         <x:v>0</x:v>
@@ -11914,7 +12609,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N48" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O48" s="72" t="b">
         <x:v>0</x:v>
@@ -12346,7 +13041,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N56" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O56" s="72" t="b">
         <x:v>0</x:v>
@@ -12402,7 +13097,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N57" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O57" s="72" t="b">
         <x:v>0</x:v>
@@ -12456,7 +13151,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N58" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O58" s="72" t="b">
         <x:v>0</x:v>
@@ -12510,7 +13205,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N59" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O59" s="72" t="b">
         <x:v>0</x:v>
@@ -12836,7 +13531,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N65" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O65" s="72" t="b">
         <x:v>0</x:v>
@@ -12886,7 +13581,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N66" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O66" s="72" t="b">
         <x:v>0</x:v>
@@ -13914,7 +14609,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N85" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O85" s="72" t="b">
         <x:v>0</x:v>
@@ -13970,7 +14665,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N86" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O86" s="72" t="b">
         <x:v>0</x:v>
@@ -14080,7 +14775,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N88" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O88" s="72" t="b">
         <x:v>0</x:v>
@@ -14134,7 +14829,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N89" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O89" s="72" t="b">
         <x:v>0</x:v>
@@ -14300,7 +14995,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N92" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O92" s="72" t="b">
         <x:v>0</x:v>
@@ -14354,7 +15049,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N93" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O93" s="72" t="b">
         <x:v>0</x:v>
@@ -14578,7 +15273,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N97" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O97" s="72" t="b">
         <x:v>0</x:v>
@@ -14744,7 +15439,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N100" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O100" s="72" t="b">
         <x:v>0</x:v>
@@ -14798,7 +15493,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N101" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O101" s="72" t="b">
         <x:v>0</x:v>
@@ -14852,7 +15547,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N102" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O102" s="72" t="b">
         <x:v>0</x:v>
@@ -15512,7 +16207,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N114" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O114" s="72" t="b">
         <x:v>0</x:v>
@@ -15568,7 +16263,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N115" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O115" s="72" t="b">
         <x:v>0</x:v>
@@ -15678,7 +16373,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N117" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O117" s="72" t="b">
         <x:v>0</x:v>
@@ -15732,7 +16427,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N118" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O118" s="72" t="b">
         <x:v>0</x:v>
@@ -16226,7 +16921,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N127" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O127" s="72" t="b">
         <x:v>0</x:v>
@@ -16282,7 +16977,7 @@
         <x:v>-59.65</x:v>
       </x:c>
       <x:c r="N128" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O128" s="72" t="b">
         <x:v>0</x:v>
@@ -16392,7 +17087,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N130" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O130" s="72" t="b">
         <x:v>0</x:v>
@@ -16446,7 +17141,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N131" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O131" s="72" t="b">
         <x:v>0</x:v>
@@ -16610,7 +17305,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N134" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O134" s="72" t="b">
         <x:v>0</x:v>
@@ -16832,7 +17527,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N138" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O138" s="72" t="b">
         <x:v>0</x:v>
@@ -17496,7 +18191,7 @@
         <x:v>-1.99</x:v>
       </x:c>
       <x:c r="N150" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O150" s="72" t="b">
         <x:v>0</x:v>
@@ -17606,7 +18301,7 @@
         <x:v>-66.44</x:v>
       </x:c>
       <x:c r="N152" s="72" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O152" s="72" t="b">
         <x:v>0</x:v>
@@ -17660,7 +18355,7 @@
         <x:v>-56.46</x:v>
       </x:c>
       <x:c r="N153" s="73" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O153" s="73" t="b">
         <x:v>0</x:v>
@@ -17682,7 +18377,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36fa8fb625b04ea2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1605427a6c12412d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
